--- a/intern_schedule_2026-2027/schedules/TYP_Intern_Schedule_Oct2026-Jun2027.xlsx
+++ b/intern_schedule_2026-2027/schedules/TYP_Intern_Schedule_Oct2026-Jun2027.xlsx
@@ -45,7 +45,7 @@
       <i val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -67,11 +67,6 @@
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -91,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -108,9 +103,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1476,9 +1468,9 @@
         </is>
       </c>
       <c r="D3" s="5" t="n"/>
-      <c r="E3" s="8" t="inlineStr">
-        <is>
-          <t>KENNEDY</t>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>WISE</t>
         </is>
       </c>
     </row>
@@ -1493,17 +1485,17 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>MULLINS, CHIASSON</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
           <t>WISE</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>MULLINS, CHIASSON</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -1523,12 +1515,12 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>WISE, CHIASSON</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>KENNEDY</t>
+          <t>KENNEDY, CHIASSON</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>WISE</t>
         </is>
       </c>
     </row>
@@ -1548,12 +1540,12 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>WISE, MULLINS</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>KENNEDY</t>
+          <t>KENNEDY, MULLINS</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>WISE</t>
         </is>
       </c>
     </row>
@@ -1576,9 +1568,9 @@
           <t>CHIASSON</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>KENNEDY</t>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>WISE</t>
         </is>
       </c>
     </row>
@@ -1593,17 +1585,17 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
+          <t>CHIASSON</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>KENNEDY, MULLINS</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
           <t>WISE</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>MULLINS, CHIASSON</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -1639,13 +1631,13 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>WISE</t>
         </is>
       </c>
       <c r="D10" s="5" t="n"/>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>WISE</t>
+          <t>CHIASSON</t>
         </is>
       </c>
     </row>
@@ -1658,19 +1650,19 @@
       <c r="B11" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>KENNEDY</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>SAEED, CHIASSON</t>
+          <t>WISE, SAEED</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>WISE</t>
+          <t>CHIASSON</t>
         </is>
       </c>
     </row>
@@ -1688,14 +1680,14 @@
           <t>SAEED</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>KENNEDY, CHIASSON</t>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>WISE, KENNEDY</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>WISE</t>
+          <t>CHIASSON</t>
         </is>
       </c>
     </row>
@@ -1710,17 +1702,17 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
+          <t>WISE</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>KENNEDY, SAEED</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
           <t>CHIASSON</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>KENNEDY, SAEED</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>WISE</t>
         </is>
       </c>
     </row>
@@ -1735,17 +1727,17 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
           <t>SAEED</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>CHIASSON</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>WISE</t>
         </is>
       </c>
     </row>
@@ -1758,19 +1750,19 @@
       <c r="B15" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>KENNEDY</t>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>SAEED</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>SAEED, CHIASSON</t>
+          <t>WISE, KENNEDY</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>WISE</t>
+          <t>CHIASSON</t>
         </is>
       </c>
     </row>
@@ -1785,13 +1777,13 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>WISE</t>
         </is>
       </c>
       <c r="D16" s="4" t="n"/>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>CHIASSON  (24H)</t>
+          <t>WISE  (24H)</t>
         </is>
       </c>
     </row>
@@ -1804,15 +1796,15 @@
       <c r="B17" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>KENNEDY</t>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>CHIASSON</t>
         </is>
       </c>
       <c r="D17" s="5" t="n"/>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>SAEED</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -1827,17 +1819,17 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>WISE</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>KENNEDY, VIVEKANANDAN</t>
+          <t>SAEED</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>WISE, VIVEKANANDAN</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>SAEED</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -1855,14 +1847,14 @@
           <t>VIVEKANANDAN</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>WISE, KENNEDY</t>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>WISE, SAEED</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>SAEED</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -1875,19 +1867,19 @@
       <c r="B20" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>WISE</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>SAEED, VIVEKANANDAN</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>KENNEDY</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>WISE, VIVEKANANDAN</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>SAEED</t>
         </is>
       </c>
     </row>
@@ -1902,7 +1894,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>WISE</t>
+          <t>SAEED</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -1912,7 +1904,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>SAEED</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -1930,14 +1922,14 @@
           <t>VIVEKANANDAN</t>
         </is>
       </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>WISE, KENNEDY</t>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>WISE, SAEED</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>SAEED</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -1952,13 +1944,13 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>WISE</t>
+          <t>SAEED</t>
         </is>
       </c>
       <c r="D23" s="4" t="n"/>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>WISE  (24H)</t>
+          <t>SAEED  (24H)</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1965,7 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>SAEED</t>
+          <t>KENNEDY</t>
         </is>
       </c>
       <c r="D24" s="5" t="n"/>
@@ -1992,14 +1984,14 @@
       <c r="B25" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>KENNEDY</t>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>WISE</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>WISE, SHETTY</t>
+          <t>KENNEDY, SHETTY</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -2022,7 +2014,7 @@
           <t>SHETTY</t>
         </is>
       </c>
-      <c r="D26" s="8" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>WISE, KENNEDY</t>
         </is>
@@ -2044,12 +2036,12 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>WISE</t>
-        </is>
-      </c>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>KENNEDY, SHETTY</t>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>WISE, SHETTY</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -2069,12 +2061,12 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
+          <t>WISE</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
           <t>SHETTY</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>WISE</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -2094,12 +2086,12 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>WISE</t>
-        </is>
-      </c>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>KENNEDY, SHETTY</t>
+          <t>SHETTY</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>WISE, KENNEDY</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -2117,13 +2109,13 @@
       <c r="B30" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="C30" s="8" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>KENNEDY</t>
         </is>
       </c>
       <c r="D30" s="4" t="n"/>
-      <c r="E30" s="8" t="inlineStr">
+      <c r="E30" s="4" t="inlineStr">
         <is>
           <t>KENNEDY  (24H)</t>
         </is>
@@ -2164,7 +2156,7 @@
           <t>WISE</t>
         </is>
       </c>
-      <c r="D32" s="8" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>KENNEDY, VIVEKANANDAN</t>
         </is>
@@ -5171,7 +5163,7 @@
           <t>MATSUOKA</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>KENNEDY, SHETTY</t>
         </is>
@@ -5191,7 +5183,7 @@
       <c r="B4" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>KENNEDY</t>
         </is>
@@ -5221,7 +5213,7 @@
           <t>SHETTY</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>KENNEDY, MATSUOKA</t>
         </is>
@@ -5241,7 +5233,7 @@
       <c r="B6" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>KENNEDY</t>
         </is>
@@ -5271,7 +5263,7 @@
           <t>MATSUOKA</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>KENNEDY, SHETTY</t>
         </is>
@@ -5318,7 +5310,7 @@
         </is>
       </c>
       <c r="D9" s="5" t="n"/>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>KENNEDY</t>
         </is>
@@ -5343,7 +5335,7 @@
           <t>SHETTY, PATEL</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>KENNEDY</t>
         </is>
@@ -5368,7 +5360,7 @@
           <t>MATSUOKA, SHETTY</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>KENNEDY</t>
         </is>
@@ -5393,7 +5385,7 @@
           <t>MATSUOKA, PATEL</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>KENNEDY</t>
         </is>
@@ -5418,7 +5410,7 @@
           <t>SHETTY</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>KENNEDY</t>
         </is>
@@ -5443,7 +5435,7 @@
           <t>SHETTY, PATEL</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>KENNEDY</t>
         </is>
@@ -5500,7 +5492,7 @@
       <c r="B17" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>KENNEDY</t>
         </is>
@@ -5530,7 +5522,7 @@
           <t>BUTT</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>KENNEDY, PATEL</t>
         </is>
@@ -5555,7 +5547,7 @@
           <t>PATEL</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>KENNEDY, BUTT</t>
         </is>
@@ -5605,7 +5597,7 @@
           <t>PATEL</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>KENNEDY, BUTT</t>
         </is>
@@ -5625,13 +5617,13 @@
       <c r="B22" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>KENNEDY</t>
         </is>
       </c>
       <c r="D22" s="4" t="n"/>
-      <c r="E22" s="8" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>KENNEDY  (24H)</t>
         </is>
@@ -5672,7 +5664,7 @@
           <t>MATSUOKA</t>
         </is>
       </c>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>KENNEDY, ALMADHOOB</t>
         </is>
@@ -5697,7 +5689,7 @@
           <t>ALMADHOOB</t>
         </is>
       </c>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>KENNEDY, MATSUOKA</t>
         </is>
@@ -5717,7 +5709,7 @@
       <c r="B26" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="C26" s="8" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>KENNEDY</t>
         </is>
@@ -5747,7 +5739,7 @@
           <t>ALMADHOOB</t>
         </is>
       </c>
-      <c r="D27" s="8" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>KENNEDY</t>
         </is>
@@ -5767,7 +5759,7 @@
       <c r="B28" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="C28" s="8" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>KENNEDY</t>
         </is>
@@ -5834,7 +5826,7 @@
       <c r="B31" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="C31" s="8" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>KENNEDY</t>
         </is>
@@ -5864,7 +5856,7 @@
           <t>RIVERA</t>
         </is>
       </c>
-      <c r="D32" s="8" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>KENNEDY, MATSUOKA</t>
         </is>
@@ -5889,7 +5881,7 @@
           <t>MATSUOKA</t>
         </is>
       </c>
-      <c r="D33" s="8" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>KENNEDY, RIVERA</t>
         </is>

--- a/intern_schedule_2026-2027/schedules/TYP_Intern_Schedule_Oct2026-Jun2027.xlsx
+++ b/intern_schedule_2026-2027/schedules/TYP_Intern_Schedule_Oct2026-Jun2027.xlsx
@@ -525,17 +525,17 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>BUTT</t>
+          <t>BUTT A</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>MACNEILLE S</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>AHLUWALIA</t>
+          <t>AHLUWALIA Sr</t>
         </is>
       </c>
     </row>
@@ -550,17 +550,17 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE, BUTT</t>
+          <t>MACNEILLE S, BUTT A</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>AHLUWALIA</t>
+          <t>AHLUWALIA Sr</t>
         </is>
       </c>
     </row>
@@ -575,13 +575,13 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>BUTT</t>
+          <t>BUTT A</t>
         </is>
       </c>
       <c r="D5" s="4" t="n"/>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>BUTT  (24H)</t>
+          <t>BUTT A  (24H)</t>
         </is>
       </c>
     </row>
@@ -596,13 +596,13 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>AHLUWALIA</t>
+          <t>AHLUWALIA Sr</t>
         </is>
       </c>
       <c r="D6" s="5" t="n"/>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>MACNEILLE S</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>BUTT, AHLUWALIA</t>
+          <t>BUTT A, AHLUWALIA Sr</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>MACNEILLE S</t>
         </is>
       </c>
     </row>
@@ -642,17 +642,17 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>BUTT</t>
+          <t>BUTT A</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>BRONSON, AHLUWALIA</t>
+          <t>BRONSON I, AHLUWALIA Sr</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>MACNEILLE S</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>AHLUWALIA</t>
+          <t>AHLUWALIA Sr</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>BRONSON, BUTT</t>
+          <t>BRONSON I, BUTT A</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>MACNEILLE S</t>
         </is>
       </c>
     </row>
@@ -692,17 +692,17 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>BUTT</t>
+          <t>BUTT A</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>AHLUWALIA</t>
+          <t>BRONSON I</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>MACNEILLE S</t>
         </is>
       </c>
     </row>
@@ -717,17 +717,17 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>BUTT, AHLUWALIA</t>
+          <t>BUTT A, AHLUWALIA Sr</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>MACNEILLE S</t>
         </is>
       </c>
     </row>
@@ -742,13 +742,13 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>AHLUWALIA</t>
+          <t>AHLUWALIA Sr</t>
         </is>
       </c>
       <c r="D12" s="4" t="n"/>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>AHLUWALIA  (24H)</t>
+          <t>AHLUWALIA Sr  (24H)</t>
         </is>
       </c>
     </row>
@@ -763,13 +763,13 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>BUTT</t>
+          <t>BUTT A</t>
         </is>
       </c>
       <c r="D13" s="5" t="n"/>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
     </row>
@@ -784,17 +784,17 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>MACNEILLE S</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>MULLINS, AHLUWALIA</t>
+          <t>MULLINS H, AHLUWALIA Sr</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>MULLINS</t>
+          <t>MULLINS H</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE, AHLUWALIA</t>
+          <t>MACNEILLE S, AHLUWALIA Sr</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
     </row>
@@ -834,17 +834,17 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>AHLUWALIA</t>
+          <t>AHLUWALIA Sr</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE, MULLINS</t>
+          <t>MACNEILLE S, MULLINS H</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>MULLINS</t>
+          <t>MULLINS H</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>AHLUWALIA</t>
+          <t>AHLUWALIA Sr</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
     </row>
@@ -884,17 +884,17 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>AHLUWALIA</t>
+          <t>AHLUWALIA Sr</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE, MULLINS</t>
+          <t>MACNEILLE S, MULLINS H</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
     </row>
@@ -909,13 +909,13 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>MACNEILLE S</t>
         </is>
       </c>
       <c r="D19" s="4" t="n"/>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE  (24H)</t>
+          <t>MACNEILLE S  (24H)</t>
         </is>
       </c>
     </row>
@@ -930,13 +930,13 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>AHLUWALIA</t>
+          <t>AHLUWALIA Sr</t>
         </is>
       </c>
       <c r="D20" s="5" t="n"/>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>MULLINS</t>
+          <t>MULLINS H</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE, CHIASSON</t>
+          <t>MACNEILLE S, CHIASSON M</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>MULLINS</t>
+          <t>MULLINS H</t>
         </is>
       </c>
     </row>
@@ -976,17 +976,17 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>CHIASSON M</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE, BRONSON</t>
+          <t>MACNEILLE S, BRONSON I</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>MULLINS</t>
+          <t>MULLINS H</t>
         </is>
       </c>
     </row>
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>MACNEILLE S</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>BRONSON, CHIASSON</t>
+          <t>BRONSON I, CHIASSON M</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>MULLINS</t>
+          <t>MULLINS H</t>
         </is>
       </c>
     </row>
@@ -1026,17 +1026,17 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>CHIASSON M</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>MULLINS</t>
+          <t>MULLINS H</t>
         </is>
       </c>
     </row>
@@ -1051,17 +1051,17 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>CHIASSON M</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE, BRONSON</t>
+          <t>MACNEILLE S, BRONSON I</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>MULLINS</t>
+          <t>MULLINS H</t>
         </is>
       </c>
     </row>
@@ -1076,13 +1076,13 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
       <c r="D26" s="4" t="n"/>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>BRONSON  (24H)</t>
+          <t>BRONSON I  (24H)</t>
         </is>
       </c>
     </row>
@@ -1097,13 +1097,13 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>MULLINS</t>
+          <t>MULLINS H</t>
         </is>
       </c>
       <c r="D27" s="5" t="n"/>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>CHIASSON M</t>
         </is>
       </c>
     </row>
@@ -1118,17 +1118,17 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>MACNEILLE S</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>BRONSON, MULLINS</t>
+          <t>BRONSON I, MULLINS H</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>CHIASSON M</t>
         </is>
       </c>
     </row>
@@ -1143,17 +1143,17 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE, MULLINS</t>
+          <t>MACNEILLE S, MULLINS H</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>CHIASSON M</t>
         </is>
       </c>
     </row>
@@ -1168,17 +1168,17 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>MULLINS</t>
+          <t>MULLINS H</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE, BRONSON</t>
+          <t>MACNEILLE S, BRONSON I</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>CHIASSON M</t>
         </is>
       </c>
     </row>
@@ -1193,17 +1193,17 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>MACNEILLE S</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>MULLINS</t>
+          <t>BRONSON I</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>CHIASSON M</t>
         </is>
       </c>
     </row>
@@ -1218,17 +1218,17 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE, MULLINS</t>
+          <t>MACNEILLE S, MULLINS H</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>CHIASSON M</t>
         </is>
       </c>
     </row>
@@ -1243,13 +1243,13 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>MULLINS</t>
+          <t>MULLINS H</t>
         </is>
       </c>
       <c r="D33" s="4" t="n"/>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>MULLINS  (24H)</t>
+          <t>MULLINS H  (24H)</t>
         </is>
       </c>
     </row>
@@ -1464,13 +1464,13 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>CHIASSON M</t>
         </is>
       </c>
       <c r="D3" s="5" t="n"/>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>WISE</t>
+          <t>WISE J</t>
         </is>
       </c>
     </row>
@@ -1485,17 +1485,17 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>KENNEDY D</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>MULLINS, CHIASSON</t>
+          <t>MULLINS H, CHIASSON M</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>WISE</t>
+          <t>WISE J</t>
         </is>
       </c>
     </row>
@@ -1510,17 +1510,17 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>MULLINS</t>
+          <t>MULLINS H</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY, CHIASSON</t>
+          <t>KENNEDY D, CHIASSON M</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>WISE</t>
+          <t>WISE J</t>
         </is>
       </c>
     </row>
@@ -1535,17 +1535,17 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>CHIASSON M</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY, MULLINS</t>
+          <t>KENNEDY D, MULLINS H</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>WISE</t>
+          <t>WISE J</t>
         </is>
       </c>
     </row>
@@ -1560,17 +1560,17 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>MULLINS</t>
+          <t>MULLINS H</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>CHIASSON M</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>WISE</t>
+          <t>WISE J</t>
         </is>
       </c>
     </row>
@@ -1585,17 +1585,17 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>CHIASSON M</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY, MULLINS</t>
+          <t>KENNEDY D, MULLINS H</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>WISE</t>
+          <t>WISE J</t>
         </is>
       </c>
     </row>
@@ -1610,13 +1610,13 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>MULLINS</t>
+          <t>MULLINS H</t>
         </is>
       </c>
       <c r="D9" s="4" t="n"/>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>MULLINS  (24H)</t>
+          <t>MULLINS H  (24H)</t>
         </is>
       </c>
     </row>
@@ -1631,13 +1631,13 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>WISE</t>
+          <t>WISE J</t>
         </is>
       </c>
       <c r="D10" s="5" t="n"/>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>CHIASSON M</t>
         </is>
       </c>
     </row>
@@ -1652,17 +1652,17 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>KENNEDY D</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>WISE, SAEED</t>
+          <t>WISE J, SAEED U</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>CHIASSON M</t>
         </is>
       </c>
     </row>
@@ -1677,17 +1677,17 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>SAEED</t>
+          <t>SAEED U</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>WISE, KENNEDY</t>
+          <t>WISE J, KENNEDY D</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>CHIASSON M</t>
         </is>
       </c>
     </row>
@@ -1702,17 +1702,17 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>WISE</t>
+          <t>WISE J</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY, SAEED</t>
+          <t>KENNEDY D, SAEED U</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>CHIASSON M</t>
         </is>
       </c>
     </row>
@@ -1727,17 +1727,17 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>KENNEDY D</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>SAEED</t>
+          <t>SAEED U</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>CHIASSON M</t>
         </is>
       </c>
     </row>
@@ -1752,17 +1752,17 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>SAEED</t>
+          <t>SAEED U</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>WISE, KENNEDY</t>
+          <t>WISE J, KENNEDY D</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>CHIASSON M</t>
         </is>
       </c>
     </row>
@@ -1777,13 +1777,13 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>WISE</t>
+          <t>WISE J</t>
         </is>
       </c>
       <c r="D16" s="4" t="n"/>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>WISE  (24H)</t>
+          <t>WISE J  (24H)</t>
         </is>
       </c>
     </row>
@@ -1798,13 +1798,13 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>CHIASSON M</t>
         </is>
       </c>
       <c r="D17" s="5" t="n"/>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>KENNEDY D</t>
         </is>
       </c>
     </row>
@@ -1819,17 +1819,17 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>SAEED</t>
+          <t>SAEED U</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>WISE, VIVEKANANDAN</t>
+          <t>WISE J, VIVEKANANDAN S</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>KENNEDY D</t>
         </is>
       </c>
     </row>
@@ -1844,17 +1844,17 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>VIVEKANANDAN</t>
+          <t>VIVEKANANDAN S</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>WISE, SAEED</t>
+          <t>WISE J, SAEED U</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>KENNEDY D</t>
         </is>
       </c>
     </row>
@@ -1869,17 +1869,17 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>WISE</t>
+          <t>WISE J</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>SAEED, VIVEKANANDAN</t>
+          <t>SAEED U, VIVEKANANDAN S</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>KENNEDY D</t>
         </is>
       </c>
     </row>
@@ -1894,17 +1894,17 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>SAEED</t>
+          <t>SAEED U</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>VIVEKANANDAN</t>
+          <t>VIVEKANANDAN S</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>KENNEDY D</t>
         </is>
       </c>
     </row>
@@ -1919,17 +1919,17 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>VIVEKANANDAN</t>
+          <t>VIVEKANANDAN S</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>WISE, SAEED</t>
+          <t>WISE J, SAEED U</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>KENNEDY D</t>
         </is>
       </c>
     </row>
@@ -1944,13 +1944,13 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>SAEED</t>
+          <t>SAEED U</t>
         </is>
       </c>
       <c r="D23" s="4" t="n"/>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>SAEED  (24H)</t>
+          <t>SAEED U  (24H)</t>
         </is>
       </c>
     </row>
@@ -1965,13 +1965,13 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>KENNEDY D</t>
         </is>
       </c>
       <c r="D24" s="5" t="n"/>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>VIVEKANANDAN</t>
+          <t>VIVEKANANDAN S</t>
         </is>
       </c>
     </row>
@@ -1986,17 +1986,17 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>WISE</t>
+          <t>WISE J</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY, SHETTY</t>
+          <t>KENNEDY D, SHETTY K</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>VIVEKANANDAN</t>
+          <t>VIVEKANANDAN S</t>
         </is>
       </c>
     </row>
@@ -2011,17 +2011,17 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>SHETTY</t>
+          <t>SHETTY K</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>WISE, KENNEDY</t>
+          <t>WISE J, KENNEDY D</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>VIVEKANANDAN</t>
+          <t>VIVEKANANDAN S</t>
         </is>
       </c>
     </row>
@@ -2036,17 +2036,17 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>KENNEDY D</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>WISE, SHETTY</t>
+          <t>WISE J, SHETTY K</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>VIVEKANANDAN</t>
+          <t>VIVEKANANDAN S</t>
         </is>
       </c>
     </row>
@@ -2061,17 +2061,17 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>WISE</t>
+          <t>WISE J</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>SHETTY</t>
+          <t>SHETTY K</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>VIVEKANANDAN</t>
+          <t>VIVEKANANDAN S</t>
         </is>
       </c>
     </row>
@@ -2086,17 +2086,17 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>SHETTY</t>
+          <t>SHETTY K</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>WISE, KENNEDY</t>
+          <t>WISE J, KENNEDY D</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>VIVEKANANDAN</t>
+          <t>VIVEKANANDAN S</t>
         </is>
       </c>
     </row>
@@ -2111,13 +2111,13 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>KENNEDY D</t>
         </is>
       </c>
       <c r="D30" s="4" t="n"/>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY  (24H)</t>
+          <t>KENNEDY D  (24H)</t>
         </is>
       </c>
     </row>
@@ -2132,13 +2132,13 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>VIVEKANANDAN</t>
+          <t>VIVEKANANDAN S</t>
         </is>
       </c>
       <c r="D31" s="5" t="n"/>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>SHETTY</t>
+          <t>SHETTY K</t>
         </is>
       </c>
     </row>
@@ -2153,17 +2153,17 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>WISE</t>
+          <t>WISE J</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY, VIVEKANANDAN</t>
+          <t>KENNEDY D</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>SHETTY</t>
+          <t>SHETTY K</t>
         </is>
       </c>
     </row>
@@ -2390,17 +2390,17 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>MACNEILLE S</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>BRONSON, VIVEKANANDAN</t>
+          <t>BRONSON I, VIVEKANANDAN S</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>SHETTY</t>
+          <t>SHETTY K</t>
         </is>
       </c>
     </row>
@@ -2415,17 +2415,17 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE, VIVEKANANDAN</t>
+          <t>MACNEILLE S, VIVEKANANDAN S</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>SHETTY</t>
+          <t>SHETTY K</t>
         </is>
       </c>
     </row>
@@ -2440,17 +2440,17 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>VIVEKANANDAN</t>
+          <t>VIVEKANANDAN S</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>SHETTY</t>
+          <t>SHETTY K</t>
         </is>
       </c>
     </row>
@@ -2465,17 +2465,17 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>MACNEILLE S</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>BRONSON, VIVEKANANDAN</t>
+          <t>BRONSON I, VIVEKANANDAN S</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>SHETTY</t>
+          <t>SHETTY K</t>
         </is>
       </c>
     </row>
@@ -2490,13 +2490,13 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>VIVEKANANDAN</t>
+          <t>VIVEKANANDAN S</t>
         </is>
       </c>
       <c r="D7" s="4" t="n"/>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>VIVEKANANDAN  (24H)</t>
+          <t>VIVEKANANDAN S  (24H)</t>
         </is>
       </c>
     </row>
@@ -2511,13 +2511,13 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>SHETTY</t>
+          <t>SHETTY K</t>
         </is>
       </c>
       <c r="D8" s="5" t="n"/>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>MACNEILLE S</t>
         </is>
       </c>
     </row>
@@ -2532,17 +2532,17 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>VILLANUEVA, VIVEKANANDAN</t>
+          <t>VILLANUEVA R, VIVEKANANDAN S</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>MACNEILLE S</t>
         </is>
       </c>
     </row>
@@ -2557,17 +2557,17 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>VILLANUEVA</t>
+          <t>VILLANUEVA R</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>BRONSON, VIVEKANANDAN</t>
+          <t>BRONSON I, VIVEKANANDAN S</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>MACNEILLE S</t>
         </is>
       </c>
     </row>
@@ -2582,17 +2582,17 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>VIVEKANANDAN</t>
+          <t>VIVEKANANDAN S</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>BRONSON, VILLANUEVA</t>
+          <t>BRONSON I, VILLANUEVA R</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>MACNEILLE S</t>
         </is>
       </c>
     </row>
@@ -2607,17 +2607,17 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>VILLANUEVA</t>
+          <t>VILLANUEVA R</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>VIVEKANANDAN</t>
+          <t>VIVEKANANDAN S</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>MACNEILLE S</t>
         </is>
       </c>
     </row>
@@ -2632,17 +2632,17 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>VILLANUEVA, VIVEKANANDAN</t>
+          <t>VILLANUEVA R, VIVEKANANDAN S</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>MACNEILLE S</t>
         </is>
       </c>
     </row>
@@ -2657,13 +2657,13 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>VILLANUEVA</t>
+          <t>VILLANUEVA R</t>
         </is>
       </c>
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>VILLANUEVA  (24H)</t>
+          <t>VILLANUEVA R  (24H)</t>
         </is>
       </c>
     </row>
@@ -2678,13 +2678,13 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>VIVEKANANDAN</t>
+          <t>VIVEKANANDAN S</t>
         </is>
       </c>
       <c r="D15" s="5" t="n"/>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
     </row>
@@ -2699,17 +2699,17 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>MACNEILLE S</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>VILLANUEVA, SALAM</t>
+          <t>VILLANUEVA R, SALAM M</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
     </row>
@@ -2724,17 +2724,17 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>SALAM</t>
+          <t>SALAM M</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE, VILLANUEVA</t>
+          <t>MACNEILLE S, VILLANUEVA R</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
     </row>
@@ -2749,17 +2749,17 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>VILLANUEVA</t>
+          <t>VILLANUEVA R</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE, SALAM</t>
+          <t>MACNEILLE S, SALAM M</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
     </row>
@@ -2774,17 +2774,17 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>SALAM</t>
+          <t>SALAM M</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>VILLANUEVA</t>
+          <t>VILLANUEVA R</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
     </row>
@@ -2799,17 +2799,17 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>VILLANUEVA</t>
+          <t>VILLANUEVA R</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE, SALAM</t>
+          <t>MACNEILLE S, SALAM M</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
     </row>
@@ -2824,13 +2824,13 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>MACNEILLE S</t>
         </is>
       </c>
       <c r="D21" s="4" t="n"/>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE  (24H)</t>
+          <t>MACNEILLE S  (24H)</t>
         </is>
       </c>
     </row>
@@ -2845,13 +2845,13 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>VILLANUEVA</t>
+          <t>VILLANUEVA R</t>
         </is>
       </c>
       <c r="D22" s="5" t="n"/>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>SALAM</t>
+          <t>SALAM M</t>
         </is>
       </c>
     </row>
@@ -2866,17 +2866,17 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE, FARZEELA</t>
+          <t>MACNEILLE S, FARZEELA F</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>SALAM</t>
+          <t>SALAM M</t>
         </is>
       </c>
     </row>
@@ -2891,17 +2891,17 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>FARZEELA</t>
+          <t>FARZEELA F</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE, BRONSON</t>
+          <t>MACNEILLE S, BRONSON I</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>SALAM</t>
+          <t>SALAM M</t>
         </is>
       </c>
     </row>
@@ -2916,17 +2916,17 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>MACNEILLE S</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>BRONSON, FARZEELA</t>
+          <t>BRONSON I, FARZEELA F</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>SALAM</t>
+          <t>SALAM M</t>
         </is>
       </c>
     </row>
@@ -2941,17 +2941,17 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>FARZEELA</t>
+          <t>FARZEELA F</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>MACNEILLE S</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>SALAM</t>
+          <t>SALAM M</t>
         </is>
       </c>
     </row>
@@ -2966,17 +2966,17 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>MACNEILLE S</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>BRONSON, FARZEELA</t>
+          <t>BRONSON I, FARZEELA F</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>SALAM</t>
+          <t>SALAM M</t>
         </is>
       </c>
     </row>
@@ -2991,13 +2991,13 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
       <c r="D28" s="4" t="n"/>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>BRONSON  (24H)</t>
+          <t>BRONSON I  (24H)</t>
         </is>
       </c>
     </row>
@@ -3012,13 +3012,13 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>SALAM</t>
+          <t>SALAM M</t>
         </is>
       </c>
       <c r="D29" s="5" t="n"/>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>FARZEELA</t>
+          <t>FARZEELA F</t>
         </is>
       </c>
     </row>
@@ -3033,17 +3033,17 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>MACNEILLE S</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>BRONSON, SALAM</t>
+          <t>BRONSON I, SALAM M</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>FARZEELA</t>
+          <t>FARZEELA F</t>
         </is>
       </c>
     </row>
@@ -3058,17 +3058,17 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE, SALAM</t>
+          <t>MACNEILLE S, SALAM M</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>FARZEELA</t>
+          <t>FARZEELA F</t>
         </is>
       </c>
     </row>
@@ -3083,17 +3083,17 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>SALAM</t>
+          <t>SALAM M</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE, BRONSON</t>
+          <t>MACNEILLE S, BRONSON I</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>FARZEELA</t>
+          <t>FARZEELA F</t>
         </is>
       </c>
     </row>
@@ -3108,17 +3108,17 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>SALAM</t>
+          <t>MACNEILLE S</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>FARZEELA</t>
+          <t>FARZEELA F</t>
         </is>
       </c>
     </row>
@@ -3357,17 +3357,17 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>OGHENESUME O</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI, SALAM</t>
+          <t>ZAIDI H, SALAM M</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>FARZEELA</t>
+          <t>FARZEELA F</t>
         </is>
       </c>
     </row>
@@ -3382,13 +3382,13 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>SALAM</t>
+          <t>SALAM M</t>
         </is>
       </c>
       <c r="D4" s="4" t="n"/>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>SALAM  (24H)</t>
+          <t>SALAM M  (24H)</t>
         </is>
       </c>
     </row>
@@ -3403,13 +3403,13 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>FARZEELA</t>
+          <t>FARZEELA F</t>
         </is>
       </c>
       <c r="D5" s="5" t="n"/>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>ZAIDI H</t>
         </is>
       </c>
     </row>
@@ -3424,17 +3424,17 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>OGHENESUME O</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>AHN, SALAM</t>
+          <t>AHN H, SALAM M</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>ZAIDI H</t>
         </is>
       </c>
     </row>
@@ -3449,17 +3449,17 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>AHN</t>
+          <t>AHN H</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME, SALAM</t>
+          <t>OGHENESUME O, SALAM M</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>ZAIDI H</t>
         </is>
       </c>
     </row>
@@ -3474,17 +3474,17 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>SALAM</t>
+          <t>SALAM M</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME, AHN</t>
+          <t>OGHENESUME O, AHN H</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>ZAIDI H</t>
         </is>
       </c>
     </row>
@@ -3499,17 +3499,17 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>AHN</t>
+          <t>AHN H</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>SALAM</t>
+          <t>SALAM M</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>ZAIDI H</t>
         </is>
       </c>
     </row>
@@ -3524,17 +3524,17 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>OGHENESUME O</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>AHN, SALAM</t>
+          <t>AHN H, SALAM M</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>ZAIDI H</t>
         </is>
       </c>
     </row>
@@ -3549,13 +3549,13 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>AHN</t>
+          <t>AHN H</t>
         </is>
       </c>
       <c r="D11" s="4" t="n"/>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>AHN  (24H)</t>
+          <t>AHN H  (24H)</t>
         </is>
       </c>
     </row>
@@ -3570,13 +3570,13 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>SALAM</t>
+          <t>SALAM M</t>
         </is>
       </c>
       <c r="D12" s="5" t="n"/>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>OGHENESUME O</t>
         </is>
       </c>
     </row>
@@ -3591,17 +3591,17 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>ZAIDI H</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>AHN, JUYAL</t>
+          <t>AHN H, JUYAL S</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>OGHENESUME O</t>
         </is>
       </c>
     </row>
@@ -3616,17 +3616,17 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>JUYAL</t>
+          <t>JUYAL S</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI, AHN</t>
+          <t>ZAIDI H, AHN H</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>OGHENESUME O</t>
         </is>
       </c>
     </row>
@@ -3641,17 +3641,17 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>AHN</t>
+          <t>AHN H</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI, JUYAL</t>
+          <t>ZAIDI H, JUYAL S</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>OGHENESUME O</t>
         </is>
       </c>
     </row>
@@ -3666,17 +3666,17 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>JUYAL</t>
+          <t>JUYAL S</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>AHN</t>
+          <t>AHN H</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>OGHENESUME O</t>
         </is>
       </c>
     </row>
@@ -3691,17 +3691,17 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>AHN</t>
+          <t>AHN H</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI, JUYAL</t>
+          <t>ZAIDI H, JUYAL S</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>OGHENESUME O</t>
         </is>
       </c>
     </row>
@@ -3716,13 +3716,13 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>ZAIDI H</t>
         </is>
       </c>
       <c r="D18" s="4" t="n"/>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>ZAIDI  (24H)</t>
+          <t>ZAIDI H  (24H)</t>
         </is>
       </c>
     </row>
@@ -3737,13 +3737,13 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>JUYAL</t>
+          <t>JUYAL S</t>
         </is>
       </c>
       <c r="D19" s="5" t="n"/>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>AHN</t>
+          <t>AHN H</t>
         </is>
       </c>
     </row>
@@ -3758,17 +3758,17 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>OGHENESUME O</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI, JUYAL</t>
+          <t>ZAIDI H, JUYAL S</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>AHN</t>
+          <t>AHN H</t>
         </is>
       </c>
     </row>
@@ -3783,17 +3783,17 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>ZAIDI H</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME, JUYAL</t>
+          <t>OGHENESUME O, JUYAL S</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>AHN</t>
+          <t>AHN H</t>
         </is>
       </c>
     </row>
@@ -3808,17 +3808,17 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>JUYAL</t>
+          <t>JUYAL S</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI, OGHENESUME</t>
+          <t>ZAIDI H, OGHENESUME O</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>AHN</t>
+          <t>AHN H</t>
         </is>
       </c>
     </row>
@@ -3833,17 +3833,17 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>ZAIDI H</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>JUYAL</t>
+          <t>JUYAL S</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>AHN</t>
+          <t>AHN H</t>
         </is>
       </c>
     </row>
@@ -3858,17 +3858,17 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>JUYAL</t>
+          <t>JUYAL S</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI, OGHENESUME</t>
+          <t>ZAIDI H, OGHENESUME O</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>AHN</t>
+          <t>AHN H</t>
         </is>
       </c>
     </row>
@@ -3883,13 +3883,13 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>OGHENESUME O</t>
         </is>
       </c>
       <c r="D25" s="4" t="n"/>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>OGHENESUME  (24H)</t>
+          <t>OGHENESUME O  (24H)</t>
         </is>
       </c>
     </row>
@@ -3904,13 +3904,13 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>AHN</t>
+          <t>AHN H</t>
         </is>
       </c>
       <c r="D26" s="5" t="n"/>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>JUYAL</t>
+          <t>JUYAL S</t>
         </is>
       </c>
     </row>
@@ -3925,17 +3925,17 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>ZAIDI H</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME, AHN</t>
+          <t>OGHENESUME O, AHN H</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>JUYAL</t>
+          <t>JUYAL S</t>
         </is>
       </c>
     </row>
@@ -3950,17 +3950,17 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>OGHENESUME O</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI, AHN</t>
+          <t>ZAIDI H, AHN H</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>JUYAL</t>
+          <t>JUYAL S</t>
         </is>
       </c>
     </row>
@@ -3975,17 +3975,17 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>AHN</t>
+          <t>AHN H</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI, OGHENESUME</t>
+          <t>ZAIDI H, OGHENESUME O</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>JUYAL</t>
+          <t>JUYAL S</t>
         </is>
       </c>
     </row>
@@ -4000,17 +4000,17 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>OGHENESUME O</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>AHN</t>
+          <t>ZAIDI H</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>JUYAL</t>
+          <t>JUYAL S</t>
         </is>
       </c>
     </row>
@@ -4025,17 +4025,17 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>ZAIDI H</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME, AHN</t>
+          <t>OGHENESUME O, AHN H</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>JUYAL</t>
+          <t>JUYAL S</t>
         </is>
       </c>
     </row>
@@ -4050,13 +4050,13 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>AHN</t>
+          <t>AHN H</t>
         </is>
       </c>
       <c r="D32" s="4" t="n"/>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>AHN  (24H)</t>
+          <t>AHN H  (24H)</t>
         </is>
       </c>
     </row>
@@ -4071,13 +4071,13 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>ZAIDI H</t>
         </is>
       </c>
       <c r="D33" s="5" t="n"/>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>JUYAL</t>
+          <t>JUYAL S</t>
         </is>
       </c>
     </row>
@@ -4292,17 +4292,17 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>LI A</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI, FARZEELA</t>
+          <t>ZAIDI H, FARZEELA F</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>JUYAL</t>
+          <t>JUYAL S</t>
         </is>
       </c>
     </row>
@@ -4317,17 +4317,17 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>FARZEELA</t>
+          <t>FARZEELA F</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI, LI</t>
+          <t>ZAIDI H, LI A</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>JUYAL</t>
+          <t>JUYAL S</t>
         </is>
       </c>
     </row>
@@ -4342,17 +4342,17 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>ZAIDI H</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>LI, FARZEELA</t>
+          <t>LI A, FARZEELA F</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>JUYAL</t>
+          <t>JUYAL S</t>
         </is>
       </c>
     </row>
@@ -4367,17 +4367,17 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>FARZEELA</t>
+          <t>FARZEELA F</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>ZAIDI H</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>JUYAL</t>
+          <t>JUYAL S</t>
         </is>
       </c>
     </row>
@@ -4392,17 +4392,17 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>LI A</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI, FARZEELA</t>
+          <t>ZAIDI H, FARZEELA F</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>JUYAL</t>
+          <t>JUYAL S</t>
         </is>
       </c>
     </row>
@@ -4417,13 +4417,13 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>FARZEELA</t>
+          <t>FARZEELA F</t>
         </is>
       </c>
       <c r="D8" s="4" t="n"/>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>FARZEELA  (24H)</t>
+          <t>FARZEELA F  (24H)</t>
         </is>
       </c>
     </row>
@@ -4438,13 +4438,13 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>JUYAL</t>
+          <t>JUYAL S</t>
         </is>
       </c>
       <c r="D9" s="5" t="n"/>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>ZAIDI H</t>
         </is>
       </c>
     </row>
@@ -4459,17 +4459,17 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>LI A</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>FARZEELA, KOPP VANUZZI</t>
+          <t>FARZEELA F, KOPP VANUZZI F</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>ZAIDI H</t>
         </is>
       </c>
     </row>
@@ -4484,17 +4484,17 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI</t>
+          <t>KOPP VANUZZI F</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>LI, FARZEELA</t>
+          <t>LI A, FARZEELA F</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>ZAIDI H</t>
         </is>
       </c>
     </row>
@@ -4509,17 +4509,17 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>FARZEELA</t>
+          <t>FARZEELA F</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>LI, KOPP VANUZZI</t>
+          <t>LI A, KOPP VANUZZI F</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>ZAIDI H</t>
         </is>
       </c>
     </row>
@@ -4534,17 +4534,17 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI</t>
+          <t>KOPP VANUZZI F</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>FARZEELA</t>
+          <t>FARZEELA F</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>ZAIDI H</t>
         </is>
       </c>
     </row>
@@ -4559,17 +4559,17 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>LI A</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>FARZEELA, KOPP VANUZZI</t>
+          <t>FARZEELA F, KOPP VANUZZI F</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>ZAIDI H</t>
         </is>
       </c>
     </row>
@@ -4584,13 +4584,13 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI</t>
+          <t>KOPP VANUZZI F</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI  (24H)</t>
+          <t>KOPP VANUZZI F  (24H)</t>
         </is>
       </c>
     </row>
@@ -4605,13 +4605,13 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>FARZEELA</t>
+          <t>FARZEELA F</t>
         </is>
       </c>
       <c r="D16" s="5" t="n"/>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>LI A</t>
         </is>
       </c>
     </row>
@@ -4626,17 +4626,17 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>ZAIDI H</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>VILLANUEVA, KOPP VANUZZI</t>
+          <t>VILLANUEVA R, KOPP VANUZZI F</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>LI A</t>
         </is>
       </c>
     </row>
@@ -4651,17 +4651,17 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>VILLANUEVA</t>
+          <t>VILLANUEVA R</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI, KOPP VANUZZI</t>
+          <t>ZAIDI H, KOPP VANUZZI F</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>LI A</t>
         </is>
       </c>
     </row>
@@ -4676,17 +4676,17 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI</t>
+          <t>KOPP VANUZZI F</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI, VILLANUEVA</t>
+          <t>ZAIDI H, VILLANUEVA R</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>LI A</t>
         </is>
       </c>
     </row>
@@ -4701,17 +4701,17 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>VILLANUEVA</t>
+          <t>VILLANUEVA R</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI</t>
+          <t>KOPP VANUZZI F</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>LI A</t>
         </is>
       </c>
     </row>
@@ -4726,17 +4726,17 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI</t>
+          <t>KOPP VANUZZI F</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI, VILLANUEVA</t>
+          <t>ZAIDI H, VILLANUEVA R</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>LI A</t>
         </is>
       </c>
     </row>
@@ -4751,13 +4751,13 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>ZAIDI H</t>
         </is>
       </c>
       <c r="D22" s="4" t="n"/>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>ZAIDI  (24H)</t>
+          <t>ZAIDI H  (24H)</t>
         </is>
       </c>
     </row>
@@ -4772,13 +4772,13 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI</t>
+          <t>KOPP VANUZZI F</t>
         </is>
       </c>
       <c r="D23" s="5" t="n"/>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>VILLANUEVA</t>
+          <t>VILLANUEVA R</t>
         </is>
       </c>
     </row>
@@ -4793,17 +4793,17 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>LI A</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI, KOPP VANUZZI</t>
+          <t>ZAIDI H, KOPP VANUZZI F</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>VILLANUEVA</t>
+          <t>VILLANUEVA R</t>
         </is>
       </c>
     </row>
@@ -4818,17 +4818,17 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>ZAIDI H</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>LI, KOPP VANUZZI</t>
+          <t>LI A, KOPP VANUZZI F</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>VILLANUEVA</t>
+          <t>VILLANUEVA R</t>
         </is>
       </c>
     </row>
@@ -4843,17 +4843,17 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI</t>
+          <t>KOPP VANUZZI F</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI, LI</t>
+          <t>ZAIDI H, LI A</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>VILLANUEVA</t>
+          <t>VILLANUEVA R</t>
         </is>
       </c>
     </row>
@@ -4868,17 +4868,17 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>ZAIDI H</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI</t>
+          <t>KOPP VANUZZI F</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>VILLANUEVA</t>
+          <t>VILLANUEVA R</t>
         </is>
       </c>
     </row>
@@ -4893,17 +4893,17 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI</t>
+          <t>KOPP VANUZZI F</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI, LI</t>
+          <t>ZAIDI H, LI A</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>VILLANUEVA</t>
+          <t>VILLANUEVA R</t>
         </is>
       </c>
     </row>
@@ -4918,13 +4918,13 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>LI A</t>
         </is>
       </c>
       <c r="D29" s="4" t="n"/>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>LI  (24H)</t>
+          <t>LI A  (24H)</t>
         </is>
       </c>
     </row>
@@ -4939,13 +4939,13 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>VILLANUEVA</t>
+          <t>VILLANUEVA R</t>
         </is>
       </c>
       <c r="D30" s="5" t="n"/>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI</t>
+          <t>KOPP VANUZZI F</t>
         </is>
       </c>
     </row>
@@ -5160,17 +5160,17 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>MATSUOKA K</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY, SHETTY</t>
+          <t>KENNEDY D, SHETTY K</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI</t>
+          <t>KOPP VANUZZI F</t>
         </is>
       </c>
     </row>
@@ -5185,17 +5185,17 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>KENNEDY D</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>MATSUOKA, SHETTY</t>
+          <t>MATSUOKA K, SHETTY K</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI</t>
+          <t>KOPP VANUZZI F</t>
         </is>
       </c>
     </row>
@@ -5210,17 +5210,17 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>SHETTY</t>
+          <t>SHETTY K</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY, MATSUOKA</t>
+          <t>KENNEDY D, MATSUOKA K</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI</t>
+          <t>KOPP VANUZZI F</t>
         </is>
       </c>
     </row>
@@ -5235,17 +5235,17 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>KENNEDY D</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>SHETTY</t>
+          <t>SHETTY K</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI</t>
+          <t>KOPP VANUZZI F</t>
         </is>
       </c>
     </row>
@@ -5260,17 +5260,17 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>MATSUOKA K</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY, SHETTY</t>
+          <t>KENNEDY D, SHETTY K</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI</t>
+          <t>KOPP VANUZZI F</t>
         </is>
       </c>
     </row>
@@ -5285,13 +5285,13 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>SHETTY</t>
+          <t>SHETTY K</t>
         </is>
       </c>
       <c r="D8" s="4" t="n"/>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>SHETTY  (24H)</t>
+          <t>SHETTY K  (24H)</t>
         </is>
       </c>
     </row>
@@ -5306,13 +5306,13 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI</t>
+          <t>KOPP VANUZZI F</t>
         </is>
       </c>
       <c r="D9" s="5" t="n"/>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>KENNEDY D</t>
         </is>
       </c>
     </row>
@@ -5327,17 +5327,17 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>MATSUOKA K</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>SHETTY, PATEL</t>
+          <t>SHETTY K, PATEL T</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>KENNEDY D</t>
         </is>
       </c>
     </row>
@@ -5352,17 +5352,17 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>PATEL</t>
+          <t>PATEL T</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>MATSUOKA, SHETTY</t>
+          <t>MATSUOKA K, SHETTY K</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>KENNEDY D</t>
         </is>
       </c>
     </row>
@@ -5377,17 +5377,17 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>SHETTY</t>
+          <t>SHETTY K</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>MATSUOKA, PATEL</t>
+          <t>MATSUOKA K, PATEL T</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>KENNEDY D</t>
         </is>
       </c>
     </row>
@@ -5402,17 +5402,17 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>PATEL</t>
+          <t>PATEL T</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>SHETTY</t>
+          <t>SHETTY K</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>KENNEDY D</t>
         </is>
       </c>
     </row>
@@ -5427,17 +5427,17 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>MATSUOKA K</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>SHETTY, PATEL</t>
+          <t>SHETTY K, PATEL T</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>KENNEDY D</t>
         </is>
       </c>
     </row>
@@ -5452,13 +5452,13 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>PATEL</t>
+          <t>PATEL T</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>PATEL  (24H)</t>
+          <t>PATEL T  (24H)</t>
         </is>
       </c>
     </row>
@@ -5473,13 +5473,13 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>SHETTY</t>
+          <t>SHETTY K</t>
         </is>
       </c>
       <c r="D16" s="5" t="n"/>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>MATSUOKA K</t>
         </is>
       </c>
     </row>
@@ -5494,17 +5494,17 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>KENNEDY D</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>BUTT, PATEL</t>
+          <t>BUTT A, PATEL T</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>MATSUOKA K</t>
         </is>
       </c>
     </row>
@@ -5519,17 +5519,17 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>BUTT</t>
+          <t>BUTT A</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY, PATEL</t>
+          <t>KENNEDY D, PATEL T</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>MATSUOKA K</t>
         </is>
       </c>
     </row>
@@ -5544,17 +5544,17 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>PATEL</t>
+          <t>PATEL T</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY, BUTT</t>
+          <t>KENNEDY D, BUTT A</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>MATSUOKA K</t>
         </is>
       </c>
     </row>
@@ -5569,17 +5569,17 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>BUTT</t>
+          <t>BUTT A</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>PATEL</t>
+          <t>PATEL T</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>MATSUOKA K</t>
         </is>
       </c>
     </row>
@@ -5594,17 +5594,17 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>PATEL</t>
+          <t>PATEL T</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY, BUTT</t>
+          <t>KENNEDY D, BUTT A</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>MATSUOKA K</t>
         </is>
       </c>
     </row>
@@ -5619,13 +5619,13 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>KENNEDY D</t>
         </is>
       </c>
       <c r="D22" s="4" t="n"/>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY  (24H)</t>
+          <t>KENNEDY D  (24H)</t>
         </is>
       </c>
     </row>
@@ -5640,13 +5640,13 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>PATEL</t>
+          <t>PATEL T</t>
         </is>
       </c>
       <c r="D23" s="5" t="n"/>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>BUTT</t>
+          <t>BUTT A</t>
         </is>
       </c>
     </row>
@@ -5661,17 +5661,17 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>MATSUOKA K</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY, ALMADHOOB</t>
+          <t>KENNEDY D, ALMADHOOB M</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>BUTT</t>
+          <t>BUTT A</t>
         </is>
       </c>
     </row>
@@ -5686,17 +5686,17 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>ALMADHOOB</t>
+          <t>ALMADHOOB M</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY, MATSUOKA</t>
+          <t>KENNEDY D, MATSUOKA K</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>BUTT</t>
+          <t>BUTT A</t>
         </is>
       </c>
     </row>
@@ -5711,17 +5711,17 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>KENNEDY D</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>MATSUOKA, ALMADHOOB</t>
+          <t>MATSUOKA K, ALMADHOOB M</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>BUTT</t>
+          <t>BUTT A</t>
         </is>
       </c>
     </row>
@@ -5736,17 +5736,17 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>ALMADHOOB</t>
+          <t>ALMADHOOB M</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>KENNEDY D</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>BUTT</t>
+          <t>BUTT A</t>
         </is>
       </c>
     </row>
@@ -5761,17 +5761,17 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>KENNEDY D</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>MATSUOKA, ALMADHOOB</t>
+          <t>MATSUOKA K, ALMADHOOB M</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>BUTT</t>
+          <t>BUTT A</t>
         </is>
       </c>
     </row>
@@ -5786,13 +5786,13 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>MATSUOKA K</t>
         </is>
       </c>
       <c r="D29" s="4" t="n"/>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>MATSUOKA  (24H)</t>
+          <t>MATSUOKA K  (24H)</t>
         </is>
       </c>
     </row>
@@ -5807,13 +5807,13 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>BUTT</t>
+          <t>BUTT A</t>
         </is>
       </c>
       <c r="D30" s="5" t="n"/>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>ALMADHOOB</t>
+          <t>ALMADHOOB M</t>
         </is>
       </c>
     </row>
@@ -5828,17 +5828,17 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>KENNEDY D</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>MATSUOKA, RIVERA</t>
+          <t>MATSUOKA K, RIVERA A</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>ALMADHOOB</t>
+          <t>ALMADHOOB M</t>
         </is>
       </c>
     </row>
@@ -5853,17 +5853,17 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>RIVERA A</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY, MATSUOKA</t>
+          <t>KENNEDY D, MATSUOKA K</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>ALMADHOOB</t>
+          <t>ALMADHOOB M</t>
         </is>
       </c>
     </row>
@@ -5878,17 +5878,17 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>MATSUOKA K</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY, RIVERA</t>
+          <t>KENNEDY D, RIVERA A</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>ALMADHOOB</t>
+          <t>ALMADHOOB M</t>
         </is>
       </c>
     </row>
@@ -6139,17 +6139,17 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>ZAIDI H</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>RIVERA A</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>ALMADHOOB</t>
+          <t>ALMADHOOB M</t>
         </is>
       </c>
     </row>
@@ -6164,17 +6164,17 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>OGHENESUME O</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI, RIVERA</t>
+          <t>ZAIDI H, RIVERA A</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>ALMADHOOB</t>
+          <t>ALMADHOOB M</t>
         </is>
       </c>
     </row>
@@ -6189,13 +6189,13 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>RIVERA A</t>
         </is>
       </c>
       <c r="D5" s="4" t="n"/>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>RIVERA  (24H)</t>
+          <t>RIVERA A  (24H)</t>
         </is>
       </c>
     </row>
@@ -6210,13 +6210,13 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>ALMADHOOB</t>
+          <t>ALMADHOOB M</t>
         </is>
       </c>
       <c r="D6" s="5" t="n"/>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>ZAIDI H</t>
         </is>
       </c>
     </row>
@@ -6231,17 +6231,17 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>OGHENESUME O</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>RIVERA, ALMADHOOB</t>
+          <t>RIVERA A, ALMADHOOB M</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>ZAIDI H</t>
         </is>
       </c>
     </row>
@@ -6256,17 +6256,17 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>RIVERA A</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME, ALMADHOOB</t>
+          <t>OGHENESUME O, ALMADHOOB M</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>ZAIDI H</t>
         </is>
       </c>
     </row>
@@ -6281,17 +6281,17 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>ALMADHOOB</t>
+          <t>ALMADHOOB M</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME, RIVERA</t>
+          <t>OGHENESUME O, RIVERA A</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>ZAIDI H</t>
         </is>
       </c>
     </row>
@@ -6306,17 +6306,17 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>RIVERA A</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>ALMADHOOB</t>
+          <t>OGHENESUME O</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>ZAIDI H</t>
         </is>
       </c>
     </row>
@@ -6331,17 +6331,17 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>OGHENESUME O</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>RIVERA, ALMADHOOB</t>
+          <t>RIVERA A, ALMADHOOB M</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>ZAIDI H</t>
         </is>
       </c>
     </row>
@@ -6356,13 +6356,13 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>ALMADHOOB</t>
+          <t>ALMADHOOB M</t>
         </is>
       </c>
       <c r="D12" s="4" t="n"/>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>ALMADHOOB  (24H)</t>
+          <t>ALMADHOOB M  (24H)</t>
         </is>
       </c>
     </row>
@@ -6377,13 +6377,13 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>RIVERA A</t>
         </is>
       </c>
       <c r="D13" s="5" t="n"/>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>OGHENESUME O</t>
         </is>
       </c>
     </row>
@@ -6398,17 +6398,17 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>ZAIDI H</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>RIVERA, ALMADHOOB</t>
+          <t>RIVERA A, ALMADHOOB M</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>OGHENESUME O</t>
         </is>
       </c>
     </row>
@@ -6423,17 +6423,17 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>ALMADHOOB</t>
+          <t>ALMADHOOB M</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI, RIVERA</t>
+          <t>ZAIDI H, RIVERA A</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>OGHENESUME O</t>
         </is>
       </c>
     </row>
@@ -6448,17 +6448,17 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>RIVERA A</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI, ALMADHOOB</t>
+          <t>ZAIDI H, ALMADHOOB M</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>OGHENESUME O</t>
         </is>
       </c>
     </row>
@@ -6473,17 +6473,17 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>ALMADHOOB</t>
+          <t>ALMADHOOB M</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>RIVERA A</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>OGHENESUME O</t>
         </is>
       </c>
     </row>
@@ -6498,17 +6498,17 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>RIVERA A</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI, ALMADHOOB</t>
+          <t>ZAIDI H, ALMADHOOB M</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>OGHENESUME O</t>
         </is>
       </c>
     </row>
@@ -6523,13 +6523,13 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>ZAIDI H</t>
         </is>
       </c>
       <c r="D19" s="4" t="n"/>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>ZAIDI  (24H)</t>
+          <t>ZAIDI H  (24H)</t>
         </is>
       </c>
     </row>
@@ -6544,13 +6544,13 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>ALMADHOOB</t>
+          <t>ALMADHOOB M</t>
         </is>
       </c>
       <c r="D20" s="5" t="n"/>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>RIVERA A</t>
         </is>
       </c>
     </row>
@@ -6565,17 +6565,17 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>OGHENESUME O</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI, AHLUWALIA</t>
+          <t>ZAIDI H, AHLUWALIA Sa</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>RIVERA A</t>
         </is>
       </c>
     </row>
@@ -6590,17 +6590,17 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>AHLUWALIA</t>
+          <t>AHLUWALIA Sa</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI, OGHENESUME</t>
+          <t>ZAIDI H, OGHENESUME O</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>RIVERA A</t>
         </is>
       </c>
     </row>
@@ -6615,17 +6615,17 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>ZAIDI H</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME, AHLUWALIA</t>
+          <t>OGHENESUME O, AHLUWALIA Sa</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>RIVERA A</t>
         </is>
       </c>
     </row>
@@ -6640,17 +6640,17 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>AHLUWALIA</t>
+          <t>AHLUWALIA Sa</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>ZAIDI H</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>RIVERA A</t>
         </is>
       </c>
     </row>
@@ -6665,17 +6665,17 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>ZAIDI H</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME, AHLUWALIA</t>
+          <t>OGHENESUME O, AHLUWALIA Sa</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>RIVERA A</t>
         </is>
       </c>
     </row>
@@ -6690,13 +6690,13 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>OGHENESUME O</t>
         </is>
       </c>
       <c r="D26" s="4" t="n"/>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>OGHENESUME  (24H)</t>
+          <t>OGHENESUME O  (24H)</t>
         </is>
       </c>
     </row>
@@ -6711,13 +6711,13 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>RIVERA A</t>
         </is>
       </c>
       <c r="D27" s="5" t="n"/>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>AHLUWALIA</t>
+          <t>AHLUWALIA Sa</t>
         </is>
       </c>
     </row>
@@ -6732,17 +6732,17 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>ZAIDI H</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME, GABALLAH</t>
+          <t>OGHENESUME O, GABALLAH B</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>AHLUWALIA</t>
+          <t>AHLUWALIA Sa</t>
         </is>
       </c>
     </row>
@@ -6757,17 +6757,17 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>GABALLAH</t>
+          <t>GABALLAH B</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI, OGHENESUME</t>
+          <t>ZAIDI H, OGHENESUME O</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>AHLUWALIA</t>
+          <t>AHLUWALIA Sa</t>
         </is>
       </c>
     </row>
@@ -6782,17 +6782,17 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>OGHENESUME O</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI, GABALLAH</t>
+          <t>ZAIDI H, GABALLAH B</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>AHLUWALIA</t>
+          <t>AHLUWALIA Sa</t>
         </is>
       </c>
     </row>
@@ -6807,17 +6807,17 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>GABALLAH</t>
+          <t>GABALLAH B</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>OGHENESUME O</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>AHLUWALIA</t>
+          <t>AHLUWALIA Sa</t>
         </is>
       </c>
     </row>
@@ -6832,17 +6832,17 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>ZAIDI H</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME, GABALLAH</t>
+          <t>OGHENESUME O, GABALLAH B</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>AHLUWALIA</t>
+          <t>AHLUWALIA Sa</t>
         </is>
       </c>
     </row>
@@ -7069,13 +7069,13 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>GABALLAH</t>
+          <t>GABALLAH B</t>
         </is>
       </c>
       <c r="D3" s="4" t="n"/>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>GABALLAH  (24H)</t>
+          <t>GABALLAH B  (24H)</t>
         </is>
       </c>
     </row>
@@ -7090,13 +7090,13 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>AHLUWALIA</t>
+          <t>AHLUWALIA Sa</t>
         </is>
       </c>
       <c r="D4" s="5" t="n"/>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>LI A</t>
         </is>
       </c>
     </row>
@@ -7111,17 +7111,17 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>GABALLAH, AHLUWALIA</t>
+          <t>GABALLAH B, AHLUWALIA Sa</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>LI A</t>
         </is>
       </c>
     </row>
@@ -7136,17 +7136,17 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>GABALLAH</t>
+          <t>GABALLAH B</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>BRONSON, AHLUWALIA</t>
+          <t>BRONSON I, AHLUWALIA Sa</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>LI A</t>
         </is>
       </c>
     </row>
@@ -7161,17 +7161,17 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>AHLUWALIA</t>
+          <t>AHLUWALIA Sa</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>BRONSON, GABALLAH</t>
+          <t>BRONSON I, GABALLAH B</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>LI A</t>
         </is>
       </c>
     </row>
@@ -7186,17 +7186,17 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>GABALLAH</t>
+          <t>GABALLAH B</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>AHLUWALIA</t>
+          <t>BRONSON I</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>LI A</t>
         </is>
       </c>
     </row>
@@ -7211,17 +7211,17 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>GABALLAH, AHLUWALIA</t>
+          <t>GABALLAH B, AHLUWALIA Sa</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>LI A</t>
         </is>
       </c>
     </row>
@@ -7236,13 +7236,13 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>AHLUWALIA</t>
+          <t>AHLUWALIA Sa</t>
         </is>
       </c>
       <c r="D10" s="4" t="n"/>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>AHLUWALIA  (24H)</t>
+          <t>AHLUWALIA Sa  (24H)</t>
         </is>
       </c>
     </row>
@@ -7257,13 +7257,13 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>GABALLAH</t>
+          <t>GABALLAH B</t>
         </is>
       </c>
       <c r="D11" s="5" t="n"/>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
     </row>
@@ -7278,17 +7278,17 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>LI A</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>METRI, AHLUWALIA</t>
+          <t>METRI N, AHLUWALIA Sa</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
     </row>
@@ -7303,17 +7303,17 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>METRI</t>
+          <t>METRI N</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>LI, AHLUWALIA</t>
+          <t>LI A, AHLUWALIA Sa</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
     </row>
@@ -7328,17 +7328,17 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>AHLUWALIA</t>
+          <t>AHLUWALIA Sa</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>LI, METRI</t>
+          <t>LI A, METRI N</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
     </row>
@@ -7353,17 +7353,17 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>METRI</t>
+          <t>METRI N</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>AHLUWALIA</t>
+          <t>AHLUWALIA Sa</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
     </row>
@@ -7378,17 +7378,17 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>LI A</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>METRI, AHLUWALIA</t>
+          <t>METRI N, AHLUWALIA Sa</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
     </row>
@@ -7403,13 +7403,13 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>AHLUWALIA</t>
+          <t>AHLUWALIA Sa</t>
         </is>
       </c>
       <c r="D17" s="4" t="n"/>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>AHLUWALIA  (24H)</t>
+          <t>AHLUWALIA Sa  (24H)</t>
         </is>
       </c>
     </row>
@@ -7424,13 +7424,13 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
       <c r="D18" s="5" t="n"/>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>METRI</t>
+          <t>METRI N</t>
         </is>
       </c>
     </row>
@@ -7445,17 +7445,17 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>LI A</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>BRONSON, SANCHEZ-ALMANZAR</t>
+          <t>BRONSON I, SANCHEZ-ALMANZAR D</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>METRI</t>
+          <t>METRI N</t>
         </is>
       </c>
     </row>
@@ -7470,17 +7470,17 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>SANCHEZ-ALMANZAR</t>
+          <t>SANCHEZ-ALMANZAR D</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>LI, BRONSON</t>
+          <t>LI A, BRONSON I</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>METRI</t>
+          <t>METRI N</t>
         </is>
       </c>
     </row>
@@ -7495,17 +7495,17 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>LI, SANCHEZ-ALMANZAR</t>
+          <t>LI A, SANCHEZ-ALMANZAR D</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>METRI</t>
+          <t>METRI N</t>
         </is>
       </c>
     </row>
@@ -7520,17 +7520,17 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>SANCHEZ-ALMANZAR</t>
+          <t>SANCHEZ-ALMANZAR D</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>METRI</t>
+          <t>METRI N</t>
         </is>
       </c>
     </row>
@@ -7545,17 +7545,17 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>LI, SANCHEZ-ALMANZAR</t>
+          <t>LI A, SANCHEZ-ALMANZAR D</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>METRI</t>
+          <t>METRI N</t>
         </is>
       </c>
     </row>
@@ -7570,13 +7570,13 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>LI A</t>
         </is>
       </c>
       <c r="D24" s="4" t="n"/>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>LI  (24H)</t>
+          <t>LI A  (24H)</t>
         </is>
       </c>
     </row>
@@ -7591,13 +7591,13 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>METRI</t>
+          <t>METRI N</t>
         </is>
       </c>
       <c r="D25" s="5" t="n"/>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>SANCHEZ-ALMANZAR</t>
+          <t>SANCHEZ-ALMANZAR D</t>
         </is>
       </c>
     </row>
@@ -7612,17 +7612,17 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>LI, SAEED</t>
+          <t>LI A, SAEED S</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>SANCHEZ-ALMANZAR</t>
+          <t>SANCHEZ-ALMANZAR D</t>
         </is>
       </c>
     </row>
@@ -7637,17 +7637,17 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>SAEED</t>
+          <t>SAEED S</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>LI, BRONSON</t>
+          <t>LI A, BRONSON I</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>SANCHEZ-ALMANZAR</t>
+          <t>SANCHEZ-ALMANZAR D</t>
         </is>
       </c>
     </row>
@@ -7662,17 +7662,17 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>LI A</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>BRONSON, SAEED</t>
+          <t>BRONSON I, SAEED S</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>SANCHEZ-ALMANZAR</t>
+          <t>SANCHEZ-ALMANZAR D</t>
         </is>
       </c>
     </row>
@@ -7687,17 +7687,17 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>SAEED</t>
+          <t>SAEED S</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>SANCHEZ-ALMANZAR</t>
+          <t>SANCHEZ-ALMANZAR D</t>
         </is>
       </c>
     </row>
@@ -7712,17 +7712,17 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>SAEED</t>
+          <t>SAEED S</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>LI, BRONSON</t>
+          <t>LI A, BRONSON I</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>SANCHEZ-ALMANZAR</t>
+          <t>SANCHEZ-ALMANZAR D</t>
         </is>
       </c>
     </row>
@@ -7737,13 +7737,13 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
       <c r="D31" s="4" t="n"/>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>BRONSON  (24H)</t>
+          <t>BRONSON I  (24H)</t>
         </is>
       </c>
     </row>
@@ -7758,13 +7758,13 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>SANCHEZ-ALMANZAR</t>
+          <t>SANCHEZ-ALMANZAR D</t>
         </is>
       </c>
       <c r="D32" s="5" t="n"/>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>SAEED</t>
+          <t>SAEED S</t>
         </is>
       </c>
     </row>
@@ -7779,17 +7779,17 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>LI A</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>BRONSON, SANCHEZ-ALMANZAR</t>
+          <t>BRONSON I, SANCHEZ-ALMANZAR D</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>SAEED</t>
+          <t>SAEED S</t>
         </is>
       </c>
     </row>
@@ -8028,17 +8028,17 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>MATSUOKA K</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME, SANCHEZ-ALMANZAR</t>
+          <t>OGHENESUME O, SANCHEZ-ALMANZAR D</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>SAEED</t>
+          <t>SAEED S</t>
         </is>
       </c>
     </row>
@@ -8053,17 +8053,17 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>OGHENESUME O</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>MATSUOKA, SANCHEZ-ALMANZAR</t>
+          <t>MATSUOKA K, SANCHEZ-ALMANZAR D</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>SAEED</t>
+          <t>SAEED S</t>
         </is>
       </c>
     </row>
@@ -8078,17 +8078,17 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>SANCHEZ-ALMANZAR</t>
+          <t>SANCHEZ-ALMANZAR D</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>OGHENESUME O</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>SAEED</t>
+          <t>SAEED S</t>
         </is>
       </c>
     </row>
@@ -8103,17 +8103,17 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>OGHENESUME O</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>MATSUOKA, SANCHEZ-ALMANZAR</t>
+          <t>MATSUOKA K, SANCHEZ-ALMANZAR D</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>SAEED</t>
+          <t>SAEED S</t>
         </is>
       </c>
     </row>
@@ -8128,13 +8128,13 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>MATSUOKA K</t>
         </is>
       </c>
       <c r="D7" s="4" t="n"/>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>MATSUOKA  (24H)</t>
+          <t>MATSUOKA K  (24H)</t>
         </is>
       </c>
     </row>
@@ -8149,13 +8149,13 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>SANCHEZ-ALMANZAR</t>
+          <t>SANCHEZ-ALMANZAR D</t>
         </is>
       </c>
       <c r="D8" s="5" t="n"/>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>OGHENESUME O</t>
         </is>
       </c>
     </row>
@@ -8170,17 +8170,17 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>SAEED</t>
+          <t>SAEED S</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>MATSUOKA, SANCHEZ-ALMANZAR</t>
+          <t>MATSUOKA K, SANCHEZ-ALMANZAR D</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>OGHENESUME O</t>
         </is>
       </c>
     </row>
@@ -8195,17 +8195,17 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>MATSUOKA K</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>SAEED, SANCHEZ-ALMANZAR</t>
+          <t>SAEED S, SANCHEZ-ALMANZAR D</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>OGHENESUME O</t>
         </is>
       </c>
     </row>
@@ -8220,17 +8220,17 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>SANCHEZ-ALMANZAR</t>
+          <t>SANCHEZ-ALMANZAR D</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>MATSUOKA, SAEED</t>
+          <t>MATSUOKA K, SAEED S</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>OGHENESUME O</t>
         </is>
       </c>
     </row>
@@ -8245,17 +8245,17 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>SAEED</t>
+          <t>SAEED S</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>SANCHEZ-ALMANZAR</t>
+          <t>MATSUOKA K</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>OGHENESUME O</t>
         </is>
       </c>
     </row>
@@ -8270,17 +8270,17 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>MATSUOKA K</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>SAEED, SANCHEZ-ALMANZAR</t>
+          <t>SAEED S, SANCHEZ-ALMANZAR D</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>OGHENESUME O</t>
         </is>
       </c>
     </row>
@@ -8295,13 +8295,13 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>SANCHEZ-ALMANZAR</t>
+          <t>SANCHEZ-ALMANZAR D</t>
         </is>
       </c>
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>SANCHEZ-ALMANZAR  (24H)</t>
+          <t>SANCHEZ-ALMANZAR D  (24H)</t>
         </is>
       </c>
     </row>
@@ -8316,13 +8316,13 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>SAEED</t>
+          <t>SAEED S</t>
         </is>
       </c>
       <c r="D15" s="5" t="n"/>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>MATSUOKA K</t>
         </is>
       </c>
     </row>
@@ -8337,17 +8337,17 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>OGHENESUME O</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>SAEED, PATEL</t>
+          <t>SAEED S, PATEL T</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>MATSUOKA K</t>
         </is>
       </c>
     </row>
@@ -8362,17 +8362,17 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>PATEL</t>
+          <t>PATEL T</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME, SAEED</t>
+          <t>OGHENESUME O, SAEED S</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>MATSUOKA K</t>
         </is>
       </c>
     </row>
@@ -8387,17 +8387,17 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>SAEED</t>
+          <t>SAEED S</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME, PATEL</t>
+          <t>OGHENESUME O, PATEL T</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>MATSUOKA K</t>
         </is>
       </c>
     </row>
@@ -8412,17 +8412,17 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>PATEL</t>
+          <t>PATEL T</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>SAEED</t>
+          <t>SAEED S</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>MATSUOKA K</t>
         </is>
       </c>
     </row>
@@ -8437,17 +8437,17 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>SAEED</t>
+          <t>SAEED S</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME, PATEL</t>
+          <t>OGHENESUME O, PATEL T</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>MATSUOKA K</t>
         </is>
       </c>
     </row>
@@ -8462,13 +8462,13 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>OGHENESUME O</t>
         </is>
       </c>
       <c r="D21" s="4" t="n"/>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>OGHENESUME  (24H)</t>
+          <t>OGHENESUME O  (24H)</t>
         </is>
       </c>
     </row>
@@ -8483,13 +8483,13 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>SAEED</t>
+          <t>SAEED S</t>
         </is>
       </c>
       <c r="D22" s="5" t="n"/>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>PATEL</t>
+          <t>PATEL T</t>
         </is>
       </c>
     </row>
@@ -8504,17 +8504,17 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>MATSUOKA K</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>OGHENESUME O</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>PATEL</t>
+          <t>PATEL T</t>
         </is>
       </c>
     </row>
@@ -8529,17 +8529,17 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>OGHENESUME O</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>MATSUOKA K</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>PATEL</t>
+          <t>PATEL T</t>
         </is>
       </c>
     </row>
@@ -8554,17 +8554,17 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>MATSUOKA K</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>OGHENESUME O</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>PATEL</t>
+          <t>PATEL T</t>
         </is>
       </c>
     </row>

--- a/intern_schedule_2026-2027/schedules/TYP_Intern_Schedule_Oct2026-Jun2027.xlsx
+++ b/intern_schedule_2026-2027/schedules/TYP_Intern_Schedule_Oct2026-Jun2027.xlsx
@@ -25,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,6 +40,7 @@
     <font>
       <b val="1"/>
     </font>
+    <font/>
     <font>
       <b val="1"/>
       <i val="1"/>
@@ -86,23 +87,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -523,19 +527,19 @@
       <c r="B3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>BUTT A</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>BUTT</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>AHLUWALIA Sr</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE</t>
         </is>
       </c>
     </row>
@@ -548,61 +552,61 @@
       <c r="B4" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S, BUTT A</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>AHLUWALIA Sr</t>
         </is>
       </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>BUTT, BRONSON</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>BUTT A</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>BUTT A  (24H)</t>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>BRONSON  (24H)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>BUTT</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>AHLUWALIA Sr</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>MACNEILLE S</t>
         </is>
       </c>
     </row>
@@ -615,19 +619,19 @@
       <c r="B7" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>BUTT A, AHLUWALIA Sr</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S</t>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON, BUTT</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>AHLUWALIA Sr</t>
         </is>
       </c>
     </row>
@@ -640,19 +644,19 @@
       <c r="B8" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>BUTT A</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I, AHLUWALIA Sr</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S</t>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE, BUTT</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>AHLUWALIA Sr</t>
         </is>
       </c>
     </row>
@@ -665,19 +669,19 @@
       <c r="B9" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>BUTT</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE, BRONSON</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>AHLUWALIA Sr</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I, BUTT A</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S</t>
         </is>
       </c>
     </row>
@@ -690,19 +694,19 @@
       <c r="B10" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>BUTT A</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S</t>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>AHLUWALIA Sr</t>
         </is>
       </c>
     </row>
@@ -715,61 +719,61 @@
       <c r="B11" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>BUTT A, AHLUWALIA Sr</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S</t>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE, BUTT</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>AHLUWALIA Sr</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="B12" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>AHLUWALIA Sr</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>AHLUWALIA Sr  (24H)</t>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>BUTT</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>BUTT  (24H)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B13" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>BUTT A</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>MACNEILLE</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
         </is>
       </c>
     </row>
@@ -782,19 +786,19 @@
       <c r="B14" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>MULLINS H, AHLUWALIA Sr</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>AHLUWALIA Sr</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>MULLINS, MACNEILLE</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
         </is>
       </c>
     </row>
@@ -807,19 +811,19 @@
       <c r="B15" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>MULLINS H</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S, AHLUWALIA Sr</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>MULLINS</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>AHLUWALIA Sr, MACNEILLE</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
         </is>
       </c>
     </row>
@@ -832,19 +836,19 @@
       <c r="B16" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>AHLUWALIA Sr</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S, MULLINS H</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>AHLUWALIA Sr, MULLINS</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
         </is>
       </c>
     </row>
@@ -857,19 +861,19 @@
       <c r="B17" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>MULLINS H</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>AHLUWALIA Sr</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>MULLINS</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
         </is>
       </c>
     </row>
@@ -882,61 +886,61 @@
       <c r="B18" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>MULLINS</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>AHLUWALIA Sr, MACNEILLE</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>MACNEILLE</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>MACNEILLE  (24H)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>SUNDAY</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>AHLUWALIA Sr</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S, MULLINS H</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>SATURDAY</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>MACNEILLE S</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="n"/>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>MACNEILLE S  (24H)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>SUNDAY</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>AHLUWALIA Sr</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>MULLINS H</t>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>MULLINS</t>
         </is>
       </c>
     </row>
@@ -949,19 +953,19 @@
       <c r="B21" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S, CHIASSON M</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>MULLINS H</t>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE, CHIASSON</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>MULLINS</t>
         </is>
       </c>
     </row>
@@ -974,19 +978,19 @@
       <c r="B22" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>CHIASSON M</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S, BRONSON I</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>MULLINS H</t>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON, CHIASSON</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>MULLINS</t>
         </is>
       </c>
     </row>
@@ -999,19 +1003,19 @@
       <c r="B23" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I, CHIASSON M</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>MULLINS H</t>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>CHIASSON</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON, MACNEILLE</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>MULLINS</t>
         </is>
       </c>
     </row>
@@ -1024,19 +1028,19 @@
       <c r="B24" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>CHIASSON M</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>MULLINS H</t>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>MULLINS</t>
         </is>
       </c>
     </row>
@@ -1049,61 +1053,61 @@
       <c r="B25" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>CHIASSON M</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S, BRONSON I</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>MULLINS H</t>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON, CHIASSON</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>MULLINS</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B26" s="4" t="n">
+      <c r="B26" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="n"/>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>BRONSON I  (24H)</t>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>CHIASSON</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>CHIASSON  (24H)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="B27" s="5" t="n">
+      <c r="B27" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>MULLINS H</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>CHIASSON M</t>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>MACNEILLE</t>
         </is>
       </c>
     </row>
@@ -1116,19 +1120,19 @@
       <c r="B28" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I, MULLINS H</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>CHIASSON M</t>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>MULLINS</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>CHIASSON, BRONSON</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE</t>
         </is>
       </c>
     </row>
@@ -1141,19 +1145,19 @@
       <c r="B29" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S, MULLINS H</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>CHIASSON M</t>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>CHIASSON</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>MULLINS, BRONSON</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE</t>
         </is>
       </c>
     </row>
@@ -1166,19 +1170,19 @@
       <c r="B30" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>MULLINS H</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S, BRONSON I</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>CHIASSON M</t>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>MULLINS, CHIASSON</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE</t>
         </is>
       </c>
     </row>
@@ -1191,19 +1195,19 @@
       <c r="B31" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>CHIASSON M</t>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>MULLINS</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>CHIASSON</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE</t>
         </is>
       </c>
     </row>
@@ -1216,57 +1220,57 @@
       <c r="B32" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S, MULLINS H</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>CHIASSON M</t>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>CHIASSON</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>MULLINS, BRONSON</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B33" s="4" t="n">
+      <c r="B33" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>MULLINS H</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="n"/>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>MULLINS H  (24H)</t>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="n"/>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>BRONSON  (24H)</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>INTERNS</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D35" s="7" t="inlineStr">
         <is>
           <t>DATES</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>LSH</t>
         </is>
@@ -1297,7 +1301,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="C40" s="6" t="inlineStr">
+      <c r="C40" s="7" t="inlineStr">
         <is>
           <t>BMC-S / BRIGHTON</t>
         </is>
@@ -1328,7 +1332,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="C44" s="6" t="inlineStr">
+      <c r="C44" s="7" t="inlineStr">
         <is>
           <t>LAHEY</t>
         </is>
@@ -1359,7 +1363,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="C48" s="6" t="inlineStr">
+      <c r="C48" s="7" t="inlineStr">
         <is>
           <t>SENIOR RESIDENT</t>
         </is>
@@ -1390,7 +1394,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="C52" s="7" t="inlineStr">
+      <c r="C52" s="8" t="inlineStr">
         <is>
           <t>SHORT CALL DOESN'T LEAVE BEFORE 4 PM, UNLESS APPROVED BY PD/APDS</t>
         </is>
@@ -1454,23 +1458,23 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>CHIASSON M</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="n"/>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>WISE J</t>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>MULLINS</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="n"/>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>CHIASSON</t>
         </is>
       </c>
     </row>
@@ -1483,19 +1487,19 @@
       <c r="B4" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>KENNEDY D</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>MULLINS H, CHIASSON M</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>WISE J</t>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>WISE</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>KENNEDY, MULLINS</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>CHIASSON</t>
         </is>
       </c>
     </row>
@@ -1508,19 +1512,19 @@
       <c r="B5" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>MULLINS H</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>KENNEDY D, CHIASSON M</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>WISE J</t>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>WISE, MULLINS</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>CHIASSON</t>
         </is>
       </c>
     </row>
@@ -1533,19 +1537,19 @@
       <c r="B6" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>CHIASSON M</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>KENNEDY D, MULLINS H</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>WISE J</t>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>MULLINS</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>WISE, KENNEDY</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>CHIASSON</t>
         </is>
       </c>
     </row>
@@ -1558,19 +1562,19 @@
       <c r="B7" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>MULLINS H</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>CHIASSON M</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>WISE J</t>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>WISE</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>CHIASSON</t>
         </is>
       </c>
     </row>
@@ -1583,61 +1587,61 @@
       <c r="B8" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>CHIASSON M</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>KENNEDY D, MULLINS H</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>WISE J</t>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>WISE, MULLINS</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>CHIASSON</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B9" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>MULLINS H</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>MULLINS H  (24H)</t>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>MULLINS</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>MULLINS  (24H)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>WISE J</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>CHIASSON M</t>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>WISE</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -1650,19 +1654,19 @@
       <c r="B11" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>KENNEDY D</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>WISE J, SAEED U</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>CHIASSON M</t>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>CHIASSON</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>SAEED U, WISE</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -1675,19 +1679,19 @@
       <c r="B12" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>SAEED U</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>WISE J, KENNEDY D</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>CHIASSON M</t>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>CHIASSON, WISE</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -1700,19 +1704,19 @@
       <c r="B13" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>WISE J</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>KENNEDY D, SAEED U</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>CHIASSON M</t>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>WISE</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>CHIASSON, SAEED U</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -1725,19 +1729,19 @@
       <c r="B14" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>KENNEDY D</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>CHIASSON</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>SAEED U</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>CHIASSON M</t>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -1750,61 +1754,61 @@
       <c r="B15" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>SAEED U</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>WISE J, KENNEDY D</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>CHIASSON M</t>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>CHIASSON, WISE</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B16" s="4" t="n">
+      <c r="B16" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>WISE J</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="n"/>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>WISE J  (24H)</t>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>WISE</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>WISE  (24H)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="B17" s="5" t="n">
+      <c r="B17" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>CHIASSON M</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>KENNEDY D</t>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>CHIASSON</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>SAEED U</t>
         </is>
       </c>
     </row>
@@ -1817,19 +1821,19 @@
       <c r="B18" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>WISE, VIVEKANANDAN</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>SAEED U</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>WISE J, VIVEKANANDAN S</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>KENNEDY D</t>
         </is>
       </c>
     </row>
@@ -1842,19 +1846,19 @@
       <c r="B19" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>VIVEKANANDAN S</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>WISE J, SAEED U</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>KENNEDY D</t>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>WISE</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>KENNEDY, VIVEKANANDAN</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>SAEED U</t>
         </is>
       </c>
     </row>
@@ -1867,19 +1871,19 @@
       <c r="B20" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>WISE J</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>SAEED U, VIVEKANANDAN S</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>KENNEDY D</t>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>VIVEKANANDAN</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>KENNEDY, WISE</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>SAEED U</t>
         </is>
       </c>
     </row>
@@ -1892,19 +1896,19 @@
       <c r="B21" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>WISE</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>SAEED U</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>VIVEKANANDAN S</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>KENNEDY D</t>
         </is>
       </c>
     </row>
@@ -1917,61 +1921,61 @@
       <c r="B22" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>VIVEKANANDAN S</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>WISE J, SAEED U</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>KENNEDY D</t>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>WISE</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>KENNEDY, VIVEKANANDAN</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>SAEED U</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B23" s="4" t="n">
+      <c r="B23" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>SAEED U</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="n"/>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>SAEED U  (24H)</t>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>VIVEKANANDAN</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>VIVEKANANDAN  (24H)</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="B24" s="5" t="n">
+      <c r="B24" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>KENNEDY D</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>VIVEKANANDAN S</t>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>WISE</t>
         </is>
       </c>
     </row>
@@ -1984,19 +1988,19 @@
       <c r="B25" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>WISE J</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>KENNEDY D, SHETTY K</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>VIVEKANANDAN S</t>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>SHETTY</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>VIVEKANANDAN, KENNEDY</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>WISE</t>
         </is>
       </c>
     </row>
@@ -2009,19 +2013,19 @@
       <c r="B26" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>SHETTY K</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>WISE J, KENNEDY D</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>VIVEKANANDAN S</t>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>VIVEKANANDAN</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>SHETTY, KENNEDY</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>WISE</t>
         </is>
       </c>
     </row>
@@ -2034,19 +2038,19 @@
       <c r="B27" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>KENNEDY D</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>WISE J, SHETTY K</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>VIVEKANANDAN S</t>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>SHETTY, VIVEKANANDAN</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>WISE</t>
         </is>
       </c>
     </row>
@@ -2059,19 +2063,19 @@
       <c r="B28" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>WISE J</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>SHETTY K</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>VIVEKANANDAN S</t>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>SHETTY</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>VIVEKANANDAN</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>WISE</t>
         </is>
       </c>
     </row>
@@ -2084,61 +2088,61 @@
       <c r="B29" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>SHETTY K</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>WISE J, KENNEDY D</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>VIVEKANANDAN S</t>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>VIVEKANANDAN</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>SHETTY, KENNEDY</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>WISE</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B30" s="4" t="n">
+      <c r="B30" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>KENNEDY D</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="n"/>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>KENNEDY D  (24H)</t>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>KENNEDY  (24H)</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="B31" s="5" t="n">
+      <c r="B31" s="6" t="n">
         <v>29</v>
       </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>VIVEKANANDAN S</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="n"/>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>SHETTY K</t>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>SHETTY</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>VIVEKANANDAN</t>
         </is>
       </c>
     </row>
@@ -2151,36 +2155,36 @@
       <c r="B32" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>WISE J</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>KENNEDY D</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>SHETTY K</t>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>WISE</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>KENNEDY, SHETTY</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>VIVEKANANDAN</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="C34" s="6" t="inlineStr">
+      <c r="C34" s="7" t="inlineStr">
         <is>
           <t>INTERNS</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
         <is>
           <t>DATES</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>LSH</t>
         </is>
@@ -2211,7 +2215,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="C39" s="6" t="inlineStr">
+      <c r="C39" s="7" t="inlineStr">
         <is>
           <t>BMC-S / BRIGHTON</t>
         </is>
@@ -2254,7 +2258,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="C44" s="6" t="inlineStr">
+      <c r="C44" s="7" t="inlineStr">
         <is>
           <t>LAHEY</t>
         </is>
@@ -2285,7 +2289,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="C48" s="6" t="inlineStr">
+      <c r="C48" s="7" t="inlineStr">
         <is>
           <t>SENIOR RESIDENT</t>
         </is>
@@ -2316,7 +2320,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="C52" s="7" t="inlineStr">
+      <c r="C52" s="8" t="inlineStr">
         <is>
           <t>SHORT CALL DOESN'T LEAVE BEFORE 4 PM, UNLESS APPROVED BY PD/APDS</t>
         </is>
@@ -2388,19 +2392,19 @@
       <c r="B3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I, VIVEKANANDAN S</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>SHETTY K</t>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE, SHETTY</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>VIVEKANANDAN</t>
         </is>
       </c>
     </row>
@@ -2413,19 +2417,19 @@
       <c r="B4" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S, VIVEKANANDAN S</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>SHETTY K</t>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>SHETTY</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE, BRONSON</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>VIVEKANANDAN</t>
         </is>
       </c>
     </row>
@@ -2438,19 +2442,19 @@
       <c r="B5" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>VIVEKANANDAN S</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>SHETTY K</t>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>VIVEKANANDAN</t>
         </is>
       </c>
     </row>
@@ -2463,61 +2467,61 @@
       <c r="B6" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I, VIVEKANANDAN S</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>SHETTY K</t>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE, SHETTY</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>VIVEKANANDAN</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>VIVEKANANDAN S</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>VIVEKANANDAN S  (24H)</t>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>SHETTY</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>SHETTY  (24H)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>SHETTY K</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>MACNEILLE S</t>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>MACNEILLE</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
         </is>
       </c>
     </row>
@@ -2530,19 +2534,19 @@
       <c r="B9" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>VILLANUEVA R, VIVEKANANDAN S</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S</t>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>VIVEKANANDAN</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>VILLANUEVA, MACNEILLE</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
         </is>
       </c>
     </row>
@@ -2555,19 +2559,19 @@
       <c r="B10" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>VILLANUEVA R</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I, VIVEKANANDAN S</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S</t>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>VILLANUEVA</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>VIVEKANANDAN, MACNEILLE</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
         </is>
       </c>
     </row>
@@ -2580,19 +2584,19 @@
       <c r="B11" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>VIVEKANANDAN S</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I, VILLANUEVA R</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S</t>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>VIVEKANANDAN, VILLANUEVA</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
         </is>
       </c>
     </row>
@@ -2605,19 +2609,19 @@
       <c r="B12" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>VILLANUEVA R</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>VIVEKANANDAN S</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S</t>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>VIVEKANANDAN</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>VILLANUEVA</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
         </is>
       </c>
     </row>
@@ -2630,61 +2634,61 @@
       <c r="B13" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>VILLANUEVA R, VIVEKANANDAN S</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S</t>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>VILLANUEVA</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>VIVEKANANDAN, MACNEILLE</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>VILLANUEVA R</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="n"/>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>VILLANUEVA R  (24H)</t>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>MACNEILLE</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>MACNEILLE  (24H)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B15" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>VIVEKANANDAN S</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>VIVEKANANDAN</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>VILLANUEVA</t>
         </is>
       </c>
     </row>
@@ -2697,19 +2701,19 @@
       <c r="B16" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>VILLANUEVA R, SALAM M</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE, SALAM</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>VILLANUEVA</t>
         </is>
       </c>
     </row>
@@ -2722,19 +2726,19 @@
       <c r="B17" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>SALAM M</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S, VILLANUEVA R</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON, SALAM</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>VILLANUEVA</t>
         </is>
       </c>
     </row>
@@ -2747,19 +2751,19 @@
       <c r="B18" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>VILLANUEVA R</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S, SALAM M</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>SALAM</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON, MACNEILLE</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>VILLANUEVA</t>
         </is>
       </c>
     </row>
@@ -2772,19 +2776,19 @@
       <c r="B19" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>SALAM M</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>VILLANUEVA R</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>VILLANUEVA</t>
         </is>
       </c>
     </row>
@@ -2797,61 +2801,61 @@
       <c r="B20" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>VILLANUEVA R</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S, SALAM M</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON, SALAM</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>VILLANUEVA</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B21" s="4" t="n">
+      <c r="B21" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>MACNEILLE S</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>MACNEILLE S  (24H)</t>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>SALAM</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>SALAM  (24H)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="B22" s="5" t="n">
+      <c r="B22" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>VILLANUEVA R</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>SALAM M</t>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>MACNEILLE</t>
         </is>
       </c>
     </row>
@@ -2864,19 +2868,19 @@
       <c r="B23" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S, FARZEELA F</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>SALAM M</t>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>FARZEELA</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>SALAM, BRONSON</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE</t>
         </is>
       </c>
     </row>
@@ -2889,19 +2893,19 @@
       <c r="B24" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>FARZEELA F</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S, BRONSON I</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>SALAM M</t>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>SALAM</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>FARZEELA, BRONSON</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE</t>
         </is>
       </c>
     </row>
@@ -2914,19 +2918,19 @@
       <c r="B25" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I, FARZEELA F</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>SALAM M</t>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>FARZEELA, SALAM</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE</t>
         </is>
       </c>
     </row>
@@ -2939,19 +2943,19 @@
       <c r="B26" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>FARZEELA F</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>SALAM M</t>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>FARZEELA</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>SALAM</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE</t>
         </is>
       </c>
     </row>
@@ -2964,61 +2968,61 @@
       <c r="B27" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I, FARZEELA F</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>SALAM M</t>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>SALAM</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>FARZEELA, BRONSON</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B28" s="4" t="n">
+      <c r="B28" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="n"/>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>BRONSON I  (24H)</t>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>BRONSON  (24H)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="B29" s="5" t="n">
+      <c r="B29" s="6" t="n">
         <v>27</v>
       </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>SALAM M</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="n"/>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>FARZEELA F</t>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>FARZEELA</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>SALAM</t>
         </is>
       </c>
     </row>
@@ -3031,19 +3035,19 @@
       <c r="B30" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I, SALAM M</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>FARZEELA F</t>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON, FARZEELA</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>SALAM</t>
         </is>
       </c>
     </row>
@@ -3056,19 +3060,19 @@
       <c r="B31" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S, SALAM M</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>FARZEELA F</t>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE, FARZEELA</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>SALAM</t>
         </is>
       </c>
     </row>
@@ -3081,19 +3085,19 @@
       <c r="B32" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>SALAM M</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S, BRONSON I</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>FARZEELA F</t>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>FARZEELA</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE, BRONSON</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>SALAM</t>
         </is>
       </c>
     </row>
@@ -3106,36 +3110,36 @@
       <c r="B33" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>FARZEELA F</t>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>SALAM</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>INTERNS</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D35" s="7" t="inlineStr">
         <is>
           <t>DATES</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>LSH</t>
         </is>
@@ -3166,7 +3170,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="C40" s="6" t="inlineStr">
+      <c r="C40" s="7" t="inlineStr">
         <is>
           <t>BMC-S / BRIGHTON</t>
         </is>
@@ -3209,7 +3213,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="C45" s="6" t="inlineStr">
+      <c r="C45" s="7" t="inlineStr">
         <is>
           <t>LAHEY</t>
         </is>
@@ -3240,7 +3244,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="C49" s="6" t="inlineStr">
+      <c r="C49" s="7" t="inlineStr">
         <is>
           <t>SENIOR RESIDENT</t>
         </is>
@@ -3283,7 +3287,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="C54" s="7" t="inlineStr">
+      <c r="C54" s="8" t="inlineStr">
         <is>
           <t>SHORT CALL DOESN'T LEAVE BEFORE 4 PM, UNLESS APPROVED BY PD/APDS</t>
         </is>
@@ -3355,61 +3359,61 @@
       <c r="B3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H, SALAM M</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>FARZEELA F</t>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>ZAIDI, FARZEELA</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>SALAM</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B4" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>SALAM M</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>SALAM M  (24H)</t>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>FARZEELA</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>FARZEELA  (24H)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>FARZEELA F</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>ZAIDI H</t>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>ZAIDI</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
         </is>
       </c>
     </row>
@@ -3422,19 +3426,19 @@
       <c r="B6" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>AHN H, SALAM M</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H</t>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>SALAM</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>AHN, ZAIDI</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
         </is>
       </c>
     </row>
@@ -3447,19 +3451,19 @@
       <c r="B7" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>AHN H</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O, SALAM M</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H</t>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>AHN</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>SALAM, ZAIDI</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
         </is>
       </c>
     </row>
@@ -3472,19 +3476,19 @@
       <c r="B8" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>SALAM M</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O, AHN H</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H</t>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>ZAIDI</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>SALAM, AHN</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
         </is>
       </c>
     </row>
@@ -3497,19 +3501,19 @@
       <c r="B9" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>AHN H</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>SALAM M</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H</t>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>SALAM</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>AHN</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
         </is>
       </c>
     </row>
@@ -3522,61 +3526,61 @@
       <c r="B10" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>AHN H, SALAM M</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H</t>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>AHN</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>SALAM, ZAIDI</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B11" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>AHN H</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>AHN H  (24H)</t>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>ZAIDI</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>ZAIDI  (24H)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>SALAM M</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>OGHENESUME O</t>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>SALAM</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>AHN</t>
         </is>
       </c>
     </row>
@@ -3589,19 +3593,19 @@
       <c r="B13" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>AHN H, JUYAL S</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O</t>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>ZAIDI, JUYAL</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>AHN</t>
         </is>
       </c>
     </row>
@@ -3614,19 +3618,19 @@
       <c r="B14" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>JUYAL S</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H, AHN H</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O</t>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>ZAIDI</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME, JUYAL</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>AHN</t>
         </is>
       </c>
     </row>
@@ -3639,19 +3643,19 @@
       <c r="B15" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>AHN H</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H, JUYAL S</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O</t>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>JUYAL</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME, ZAIDI</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>AHN</t>
         </is>
       </c>
     </row>
@@ -3664,19 +3668,19 @@
       <c r="B16" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>JUYAL S</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>AHN H</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O</t>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>ZAIDI</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>AHN</t>
         </is>
       </c>
     </row>
@@ -3689,61 +3693,61 @@
       <c r="B17" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>AHN H</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H, JUYAL S</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O</t>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>ZAIDI</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME, JUYAL</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>AHN</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B18" s="4" t="n">
+      <c r="B18" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>ZAIDI H</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="n"/>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>ZAIDI H  (24H)</t>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>JUYAL</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>JUYAL  (24H)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="B19" s="5" t="n">
+      <c r="B19" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>JUYAL S</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>AHN H</t>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>ZAIDI</t>
         </is>
       </c>
     </row>
@@ -3756,19 +3760,19 @@
       <c r="B20" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H, JUYAL S</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>AHN H</t>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>AHN</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>JUYAL, OGHENESUME</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>ZAIDI</t>
         </is>
       </c>
     </row>
@@ -3781,19 +3785,19 @@
       <c r="B21" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O, JUYAL S</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>AHN H</t>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>JUYAL</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>AHN, OGHENESUME</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>ZAIDI</t>
         </is>
       </c>
     </row>
@@ -3806,19 +3810,19 @@
       <c r="B22" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>JUYAL S</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H, OGHENESUME O</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>AHN H</t>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>AHN, JUYAL</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>ZAIDI</t>
         </is>
       </c>
     </row>
@@ -3831,19 +3835,19 @@
       <c r="B23" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>JUYAL S</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>AHN H</t>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>AHN</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>JUYAL</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>ZAIDI</t>
         </is>
       </c>
     </row>
@@ -3856,61 +3860,61 @@
       <c r="B24" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>JUYAL S</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H, OGHENESUME O</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>AHN H</t>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>JUYAL</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>AHN, OGHENESUME</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>ZAIDI</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B25" s="4" t="n">
+      <c r="B25" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>OGHENESUME O</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="n"/>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>OGHENESUME O  (24H)</t>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>OGHENESUME  (24H)</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="B26" s="5" t="n">
+      <c r="B26" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>AHN H</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>JUYAL S</t>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>AHN</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>JUYAL</t>
         </is>
       </c>
     </row>
@@ -3923,19 +3927,19 @@
       <c r="B27" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O, AHN H</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>JUYAL S</t>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>ZAIDI</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME, AHN</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>JUYAL</t>
         </is>
       </c>
     </row>
@@ -3948,19 +3952,19 @@
       <c r="B28" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H, AHN H</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>JUYAL S</t>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>ZAIDI, AHN</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>JUYAL</t>
         </is>
       </c>
     </row>
@@ -3973,19 +3977,19 @@
       <c r="B29" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>AHN H</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H, OGHENESUME O</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>JUYAL S</t>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>AHN</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>ZAIDI, OGHENESUME</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>JUYAL</t>
         </is>
       </c>
     </row>
@@ -3998,19 +4002,19 @@
       <c r="B30" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>JUYAL S</t>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>ZAIDI</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>JUYAL</t>
         </is>
       </c>
     </row>
@@ -4023,78 +4027,78 @@
       <c r="B31" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O, AHN H</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>JUYAL S</t>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>ZAIDI, AHN</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>JUYAL</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B32" s="4" t="n">
+      <c r="B32" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>AHN H</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="n"/>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>AHN H  (24H)</t>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>AHN</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="n"/>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>AHN  (24H)</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="B33" s="5" t="n">
+      <c r="B33" s="6" t="n">
         <v>31</v>
       </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>ZAIDI H</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="n"/>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>JUYAL S</t>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>ZAIDI</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>INTERNS</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D35" s="7" t="inlineStr">
         <is>
           <t>DATES</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>LSH</t>
         </is>
@@ -4125,7 +4129,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="C40" s="6" t="inlineStr">
+      <c r="C40" s="7" t="inlineStr">
         <is>
           <t>BMC-S / BRIGHTON</t>
         </is>
@@ -4156,7 +4160,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="C44" s="6" t="inlineStr">
+      <c r="C44" s="7" t="inlineStr">
         <is>
           <t>LAHEY</t>
         </is>
@@ -4187,7 +4191,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="C48" s="6" t="inlineStr">
+      <c r="C48" s="7" t="inlineStr">
         <is>
           <t>SENIOR RESIDENT</t>
         </is>
@@ -4218,7 +4222,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="C52" s="7" t="inlineStr">
+      <c r="C52" s="8" t="inlineStr">
         <is>
           <t>SHORT CALL DOESN'T LEAVE BEFORE 4 PM, UNLESS APPROVED BY PD/APDS</t>
         </is>
@@ -4290,19 +4294,19 @@
       <c r="B3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>LI A</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H, FARZEELA F</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>JUYAL S</t>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>JUYAL</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FARZEELA, ZAIDI</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>LI</t>
         </is>
       </c>
     </row>
@@ -4315,19 +4319,19 @@
       <c r="B4" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>FARZEELA F</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H, LI A</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>JUYAL S</t>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>FARZEELA</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>JUYAL, ZAIDI</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>LI</t>
         </is>
       </c>
     </row>
@@ -4340,19 +4344,19 @@
       <c r="B5" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>LI A, FARZEELA F</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>JUYAL S</t>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>ZAIDI</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>JUYAL, FARZEELA</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>LI</t>
         </is>
       </c>
     </row>
@@ -4365,19 +4369,19 @@
       <c r="B6" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>FARZEELA F</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>JUYAL S</t>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>JUYAL</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>FARZEELA</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>LI</t>
         </is>
       </c>
     </row>
@@ -4390,61 +4394,61 @@
       <c r="B7" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>LI A</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H, FARZEELA F</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>JUYAL S</t>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>FARZEELA</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>JUYAL, ZAIDI</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>LI</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B8" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>FARZEELA F</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="n"/>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>FARZEELA F  (24H)</t>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>ZAIDI</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>ZAIDI  (24H)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>JUYAL S</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>ZAIDI H</t>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>JUYAL</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>FARZEELA</t>
         </is>
       </c>
     </row>
@@ -4457,19 +4461,19 @@
       <c r="B10" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>LI A</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>FARZEELA F, KOPP VANUZZI F</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H</t>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>ZAIDI, KOPP VANUZZI</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>FARZEELA</t>
         </is>
       </c>
     </row>
@@ -4482,19 +4486,19 @@
       <c r="B11" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>KOPP VANUZZI F</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>LI A, FARZEELA F</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H</t>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>ZAIDI</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>LI, KOPP VANUZZI</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>FARZEELA</t>
         </is>
       </c>
     </row>
@@ -4507,19 +4511,19 @@
       <c r="B12" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>FARZEELA F</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>LI A, KOPP VANUZZI F</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H</t>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>KOPP VANUZZI</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>LI, ZAIDI</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>FARZEELA</t>
         </is>
       </c>
     </row>
@@ -4532,19 +4536,19 @@
       <c r="B13" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>KOPP VANUZZI F</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>FARZEELA F</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H</t>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>ZAIDI</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>FARZEELA</t>
         </is>
       </c>
     </row>
@@ -4557,61 +4561,61 @@
       <c r="B14" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>LI A</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>FARZEELA F, KOPP VANUZZI F</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H</t>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>ZAIDI</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>LI, KOPP VANUZZI</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>FARZEELA</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n">
+      <c r="B15" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>KOPP VANUZZI F</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="n"/>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>KOPP VANUZZI F  (24H)</t>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>KOPP VANUZZI</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>KOPP VANUZZI  (24H)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="B16" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>FARZEELA F</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>LI A</t>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>ZAIDI</t>
         </is>
       </c>
     </row>
@@ -4624,19 +4628,19 @@
       <c r="B17" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>VILLANUEVA R, KOPP VANUZZI F</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>LI A</t>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>VILLANUEVA</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>KOPP VANUZZI, LI</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>ZAIDI</t>
         </is>
       </c>
     </row>
@@ -4649,19 +4653,19 @@
       <c r="B18" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>VILLANUEVA R</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H, KOPP VANUZZI F</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>LI A</t>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>KOPP VANUZZI</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>VILLANUEVA, LI</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>ZAIDI</t>
         </is>
       </c>
     </row>
@@ -4674,19 +4678,19 @@
       <c r="B19" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>KOPP VANUZZI F</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H, VILLANUEVA R</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>LI A</t>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>VILLANUEVA, KOPP VANUZZI</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>ZAIDI</t>
         </is>
       </c>
     </row>
@@ -4699,19 +4703,19 @@
       <c r="B20" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>VILLANUEVA R</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>KOPP VANUZZI F</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>LI A</t>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>VILLANUEVA</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>KOPP VANUZZI</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>ZAIDI</t>
         </is>
       </c>
     </row>
@@ -4724,61 +4728,61 @@
       <c r="B21" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>KOPP VANUZZI F</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H, VILLANUEVA R</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>LI A</t>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>KOPP VANUZZI</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>VILLANUEVA, LI</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>ZAIDI</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B22" s="4" t="n">
+      <c r="B22" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>ZAIDI H</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="n"/>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>ZAIDI H  (24H)</t>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>LI  (24H)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="B23" s="5" t="n">
+      <c r="B23" s="6" t="n">
         <v>21</v>
       </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>KOPP VANUZZI F</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>VILLANUEVA R</t>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>VILLANUEVA</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>KOPP VANUZZI</t>
         </is>
       </c>
     </row>
@@ -4791,19 +4795,19 @@
       <c r="B24" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>LI A</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H, KOPP VANUZZI F</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>VILLANUEVA R</t>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>ZAIDI</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>LI, VILLANUEVA</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>KOPP VANUZZI</t>
         </is>
       </c>
     </row>
@@ -4816,19 +4820,19 @@
       <c r="B25" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>LI A, KOPP VANUZZI F</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>VILLANUEVA R</t>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>ZAIDI, VILLANUEVA</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>KOPP VANUZZI</t>
         </is>
       </c>
     </row>
@@ -4841,19 +4845,19 @@
       <c r="B26" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>KOPP VANUZZI F</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H, LI A</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>VILLANUEVA R</t>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>VILLANUEVA</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>ZAIDI, LI</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>KOPP VANUZZI</t>
         </is>
       </c>
     </row>
@@ -4866,19 +4870,19 @@
       <c r="B27" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>KOPP VANUZZI F</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>VILLANUEVA R</t>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>ZAIDI</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>KOPP VANUZZI</t>
         </is>
       </c>
     </row>
@@ -4891,78 +4895,78 @@
       <c r="B28" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>KOPP VANUZZI F</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H, LI A</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>VILLANUEVA R</t>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>ZAIDI, VILLANUEVA</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>KOPP VANUZZI</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B29" s="4" t="n">
+      <c r="B29" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>LI A</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="n"/>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>LI A  (24H)</t>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>VILLANUEVA</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>VILLANUEVA  (24H)</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="B30" s="5" t="n">
+      <c r="B30" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>VILLANUEVA R</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>KOPP VANUZZI F</t>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>ZAIDI</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>LI</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>INTERNS</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t>DATES</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>LSH</t>
         </is>
@@ -4993,7 +4997,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="C37" s="6" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>BMC-S / BRIGHTON</t>
         </is>
@@ -5024,7 +5028,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="C41" s="6" t="inlineStr">
+      <c r="C41" s="7" t="inlineStr">
         <is>
           <t>LAHEY</t>
         </is>
@@ -5055,7 +5059,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="C45" s="6" t="inlineStr">
+      <c r="C45" s="7" t="inlineStr">
         <is>
           <t>SENIOR RESIDENT</t>
         </is>
@@ -5086,7 +5090,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="C49" s="7" t="inlineStr">
+      <c r="C49" s="8" t="inlineStr">
         <is>
           <t>SHORT CALL DOESN'T LEAVE BEFORE 4 PM, UNLESS APPROVED BY PD/APDS</t>
         </is>
@@ -5158,19 +5162,19 @@
       <c r="B3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>MATSUOKA K</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>KENNEDY D, SHETTY K</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>KOPP VANUZZI F</t>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>KOPP VANUZZI</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>SHETTY, KENNEDY</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>MATSUOKA</t>
         </is>
       </c>
     </row>
@@ -5183,19 +5187,19 @@
       <c r="B4" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>KENNEDY D</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>MATSUOKA K, SHETTY K</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>KOPP VANUZZI F</t>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>SHETTY</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>KOPP VANUZZI, KENNEDY</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>MATSUOKA</t>
         </is>
       </c>
     </row>
@@ -5208,19 +5212,19 @@
       <c r="B5" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>SHETTY K</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>KENNEDY D, MATSUOKA K</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>KOPP VANUZZI F</t>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>KOPP VANUZZI, SHETTY</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>MATSUOKA</t>
         </is>
       </c>
     </row>
@@ -5233,19 +5237,19 @@
       <c r="B6" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>KENNEDY D</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>SHETTY K</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>KOPP VANUZZI F</t>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>KOPP VANUZZI</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>SHETTY</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>MATSUOKA</t>
         </is>
       </c>
     </row>
@@ -5258,61 +5262,61 @@
       <c r="B7" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>MATSUOKA K</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>KENNEDY D, SHETTY K</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>KOPP VANUZZI F</t>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>SHETTY</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>KOPP VANUZZI, KENNEDY</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>MATSUOKA</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B8" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>SHETTY K</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="n"/>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>SHETTY K  (24H)</t>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>KENNEDY  (24H)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>KOPP VANUZZI F</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>KENNEDY D</t>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>KOPP VANUZZI</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>SHETTY</t>
         </is>
       </c>
     </row>
@@ -5325,19 +5329,19 @@
       <c r="B10" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>MATSUOKA K</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>SHETTY K, PATEL T</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>KENNEDY D</t>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>MATSUOKA</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>KENNEDY, PATEL</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>SHETTY</t>
         </is>
       </c>
     </row>
@@ -5350,19 +5354,19 @@
       <c r="B11" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>PATEL T</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>MATSUOKA K, SHETTY K</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>KENNEDY D</t>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>MATSUOKA, PATEL</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>SHETTY</t>
         </is>
       </c>
     </row>
@@ -5375,19 +5379,19 @@
       <c r="B12" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>SHETTY K</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>MATSUOKA K, PATEL T</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>KENNEDY D</t>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>PATEL</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>MATSUOKA, KENNEDY</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>SHETTY</t>
         </is>
       </c>
     </row>
@@ -5400,19 +5404,19 @@
       <c r="B13" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>PATEL T</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>SHETTY K</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>KENNEDY D</t>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>MATSUOKA</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>SHETTY</t>
         </is>
       </c>
     </row>
@@ -5425,61 +5429,61 @@
       <c r="B14" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>MATSUOKA K</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>SHETTY K, PATEL T</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>KENNEDY D</t>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>MATSUOKA, PATEL</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>SHETTY</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n">
+      <c r="B15" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>PATEL T</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="n"/>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>PATEL T  (24H)</t>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>PATEL</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>PATEL  (24H)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="B16" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>SHETTY K</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>MATSUOKA K</t>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>MATSUOKA</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -5492,19 +5496,19 @@
       <c r="B17" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>KENNEDY D</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>BUTT A, PATEL T</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>MATSUOKA K</t>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>BUTT</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>PATEL, MATSUOKA</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -5517,19 +5521,19 @@
       <c r="B18" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>BUTT A</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>KENNEDY D, PATEL T</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>MATSUOKA K</t>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>PATEL</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>BUTT, MATSUOKA</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -5542,19 +5546,19 @@
       <c r="B19" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>PATEL T</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>KENNEDY D, BUTT A</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>MATSUOKA K</t>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>MATSUOKA</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>BUTT, PATEL</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -5567,19 +5571,19 @@
       <c r="B20" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>BUTT A</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>PATEL T</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>MATSUOKA K</t>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>BUTT</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>PATEL</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -5592,61 +5596,61 @@
       <c r="B21" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>PATEL T</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>KENNEDY D, BUTT A</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>MATSUOKA K</t>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>PATEL</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>BUTT, MATSUOKA</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B22" s="4" t="n">
+      <c r="B22" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>KENNEDY D</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="n"/>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>KENNEDY D  (24H)</t>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>MATSUOKA</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>MATSUOKA  (24H)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="B23" s="5" t="n">
+      <c r="B23" s="6" t="n">
         <v>21</v>
       </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>PATEL T</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>BUTT A</t>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>BUTT</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>PATEL</t>
         </is>
       </c>
     </row>
@@ -5659,19 +5663,19 @@
       <c r="B24" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>MATSUOKA K</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>KENNEDY D, ALMADHOOB M</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>BUTT A</t>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>MATSUOKA, BUTT</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>ALMADHOOB</t>
         </is>
       </c>
     </row>
@@ -5684,19 +5688,19 @@
       <c r="B25" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>ALMADHOOB M</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>KENNEDY D, MATSUOKA K</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>BUTT A</t>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>MATSUOKA</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>KENNEDY, BUTT</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>ALMADHOOB</t>
         </is>
       </c>
     </row>
@@ -5709,19 +5713,19 @@
       <c r="B26" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>KENNEDY D</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>MATSUOKA K, ALMADHOOB M</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>BUTT A</t>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>BUTT</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>KENNEDY, MATSUOKA</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>ALMADHOOB</t>
         </is>
       </c>
     </row>
@@ -5734,19 +5738,19 @@
       <c r="B27" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>ALMADHOOB M</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>KENNEDY D</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>BUTT A</t>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>MATSUOKA</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>ALMADHOOB</t>
         </is>
       </c>
     </row>
@@ -5759,61 +5763,61 @@
       <c r="B28" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>KENNEDY D</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>MATSUOKA K, ALMADHOOB M</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>BUTT A</t>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>MATSUOKA</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>KENNEDY, BUTT</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>ALMADHOOB</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B29" s="4" t="n">
+      <c r="B29" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>MATSUOKA K</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="n"/>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>MATSUOKA K  (24H)</t>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>BUTT</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>BUTT  (24H)</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="B30" s="5" t="n">
+      <c r="B30" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>BUTT A</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>ALMADHOOB M</t>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>MATSUOKA</t>
         </is>
       </c>
     </row>
@@ -5826,19 +5830,19 @@
       <c r="B31" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>KENNEDY D</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>MATSUOKA K, RIVERA A</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>ALMADHOOB M</t>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>ALMADHOOB</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>RIVERA, KENNEDY</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>MATSUOKA</t>
         </is>
       </c>
     </row>
@@ -5851,19 +5855,19 @@
       <c r="B32" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>RIVERA A</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>KENNEDY D, MATSUOKA K</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>ALMADHOOB M</t>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>RIVERA</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>ALMADHOOB, KENNEDY</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>MATSUOKA</t>
         </is>
       </c>
     </row>
@@ -5876,36 +5880,36 @@
       <c r="B33" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>MATSUOKA K</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>KENNEDY D, RIVERA A</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>ALMADHOOB M</t>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>ALMADHOOB, RIVERA</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>MATSUOKA</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>INTERNS</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D35" s="7" t="inlineStr">
         <is>
           <t>DATES</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>LSH</t>
         </is>
@@ -5936,7 +5940,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="C40" s="6" t="inlineStr">
+      <c r="C40" s="7" t="inlineStr">
         <is>
           <t>BMC-S / BRIGHTON</t>
         </is>
@@ -5979,7 +5983,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="C45" s="6" t="inlineStr">
+      <c r="C45" s="7" t="inlineStr">
         <is>
           <t>LAHEY</t>
         </is>
@@ -6022,7 +6026,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="C50" s="6" t="inlineStr">
+      <c r="C50" s="7" t="inlineStr">
         <is>
           <t>SENIOR RESIDENT</t>
         </is>
@@ -6065,7 +6069,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="C55" s="7" t="inlineStr">
+      <c r="C55" s="8" t="inlineStr">
         <is>
           <t>SHORT CALL DOESN'T LEAVE BEFORE 4 PM, UNLESS APPROVED BY PD/APDS</t>
         </is>
@@ -6137,19 +6141,19 @@
       <c r="B3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>RIVERA A</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>ALMADHOOB M</t>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>ALMADHOOB</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>RIVERA</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
         </is>
       </c>
     </row>
@@ -6162,61 +6166,61 @@
       <c r="B4" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H, RIVERA A</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>ALMADHOOB M</t>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>RIVERA</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>ALMADHOOB, ZAIDI</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>RIVERA A</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>RIVERA A  (24H)</t>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>ZAIDI</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>ZAIDI  (24H)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>ALMADHOOB M</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>ZAIDI H</t>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>ALMADHOOB</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>RIVERA</t>
         </is>
       </c>
     </row>
@@ -6229,19 +6233,19 @@
       <c r="B7" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>RIVERA A, ALMADHOOB M</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H</t>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>ZAIDI, ALMADHOOB</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>RIVERA</t>
         </is>
       </c>
     </row>
@@ -6254,19 +6258,19 @@
       <c r="B8" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>RIVERA A</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O, ALMADHOOB M</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H</t>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>ZAIDI</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME, ALMADHOOB</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>RIVERA</t>
         </is>
       </c>
     </row>
@@ -6279,19 +6283,19 @@
       <c r="B9" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>ALMADHOOB M</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O, RIVERA A</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H</t>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>ALMADHOOB</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME, ZAIDI</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>RIVERA</t>
         </is>
       </c>
     </row>
@@ -6304,19 +6308,19 @@
       <c r="B10" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>RIVERA A</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H</t>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>ZAIDI</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>RIVERA</t>
         </is>
       </c>
     </row>
@@ -6329,61 +6333,61 @@
       <c r="B11" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>RIVERA A, ALMADHOOB M</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H</t>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>ZAIDI</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME, ALMADHOOB</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>RIVERA</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="B12" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>ALMADHOOB M</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>ALMADHOOB M  (24H)</t>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>ALMADHOOB</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>ALMADHOOB  (24H)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B13" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>RIVERA A</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>OGHENESUME O</t>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>ZAIDI</t>
         </is>
       </c>
     </row>
@@ -6396,19 +6400,19 @@
       <c r="B14" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>RIVERA A, ALMADHOOB M</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O</t>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>RIVERA</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>ALMADHOOB, OGHENESUME</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>ZAIDI</t>
         </is>
       </c>
     </row>
@@ -6421,19 +6425,19 @@
       <c r="B15" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>ALMADHOOB M</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H, RIVERA A</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O</t>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>ALMADHOOB</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>RIVERA, OGHENESUME</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>ZAIDI</t>
         </is>
       </c>
     </row>
@@ -6446,19 +6450,19 @@
       <c r="B16" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>RIVERA A</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H, ALMADHOOB M</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O</t>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>RIVERA, ALMADHOOB</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>ZAIDI</t>
         </is>
       </c>
     </row>
@@ -6471,19 +6475,19 @@
       <c r="B17" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>ALMADHOOB M</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>RIVERA A</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O</t>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>RIVERA</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>ALMADHOOB</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>ZAIDI</t>
         </is>
       </c>
     </row>
@@ -6496,61 +6500,61 @@
       <c r="B18" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>RIVERA A</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H, ALMADHOOB M</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O</t>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>ALMADHOOB</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>RIVERA, OGHENESUME</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>ZAIDI</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B19" s="4" t="n">
+      <c r="B19" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>ZAIDI H</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="n"/>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>ZAIDI H  (24H)</t>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>OGHENESUME  (24H)</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="B20" s="5" t="n">
+      <c r="B20" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>ALMADHOOB M</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>RIVERA A</t>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>RIVERA</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>ALMADHOOB</t>
         </is>
       </c>
     </row>
@@ -6563,19 +6567,19 @@
       <c r="B21" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H, AHLUWALIA Sa</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>RIVERA A</t>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>ZAIDI</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME, RIVERA</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>AHLUWALIA Sa</t>
         </is>
       </c>
     </row>
@@ -6588,19 +6592,19 @@
       <c r="B22" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>ZAIDI, RIVERA</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>AHLUWALIA Sa</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H, OGHENESUME O</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>RIVERA A</t>
         </is>
       </c>
     </row>
@@ -6613,19 +6617,19 @@
       <c r="B23" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O, AHLUWALIA Sa</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>RIVERA A</t>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>RIVERA</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>ZAIDI, OGHENESUME</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>AHLUWALIA Sa</t>
         </is>
       </c>
     </row>
@@ -6638,19 +6642,19 @@
       <c r="B24" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>ZAIDI</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>AHLUWALIA Sa</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>RIVERA A</t>
         </is>
       </c>
     </row>
@@ -6663,61 +6667,61 @@
       <c r="B25" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O, AHLUWALIA Sa</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>RIVERA A</t>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>ZAIDI, RIVERA</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>AHLUWALIA Sa</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B26" s="4" t="n">
+      <c r="B26" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>OGHENESUME O</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="n"/>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>OGHENESUME O  (24H)</t>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>RIVERA</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>RIVERA  (24H)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="B27" s="5" t="n">
+      <c r="B27" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>RIVERA A</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>AHLUWALIA Sa</t>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>ZAIDI</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
         </is>
       </c>
     </row>
@@ -6730,19 +6734,19 @@
       <c r="B28" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O, GABALLAH B</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>AHLUWALIA Sa</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>GABALLAH, ZAIDI</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
         </is>
       </c>
     </row>
@@ -6755,19 +6759,19 @@
       <c r="B29" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>GABALLAH B</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H, OGHENESUME O</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>AHLUWALIA Sa</t>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>GABALLAH</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>AHLUWALIA Sa, ZAIDI</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
         </is>
       </c>
     </row>
@@ -6780,19 +6784,19 @@
       <c r="B30" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H, GABALLAH B</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>AHLUWALIA Sa</t>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>ZAIDI</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>AHLUWALIA Sa, GABALLAH</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
         </is>
       </c>
     </row>
@@ -6805,19 +6809,19 @@
       <c r="B31" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>GABALLAH B</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>AHLUWALIA Sa</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>GABALLAH</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
         </is>
       </c>
     </row>
@@ -6830,36 +6834,36 @@
       <c r="B32" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O, GABALLAH B</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>AHLUWALIA Sa</t>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>GABALLAH</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>AHLUWALIA Sa, ZAIDI</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="C34" s="6" t="inlineStr">
+      <c r="C34" s="7" t="inlineStr">
         <is>
           <t>INTERNS</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
         <is>
           <t>DATES</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>LSH</t>
         </is>
@@ -6890,7 +6894,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="C39" s="6" t="inlineStr">
+      <c r="C39" s="7" t="inlineStr">
         <is>
           <t>BMC-S / BRIGHTON</t>
         </is>
@@ -6921,7 +6925,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="C43" s="6" t="inlineStr">
+      <c r="C43" s="7" t="inlineStr">
         <is>
           <t>LAHEY</t>
         </is>
@@ -6952,7 +6956,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="C47" s="6" t="inlineStr">
+      <c r="C47" s="7" t="inlineStr">
         <is>
           <t>SENIOR RESIDENT</t>
         </is>
@@ -6995,7 +6999,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="C52" s="7" t="inlineStr">
+      <c r="C52" s="8" t="inlineStr">
         <is>
           <t>SHORT CALL DOESN'T LEAVE BEFORE 4 PM, UNLESS APPROVED BY PD/APDS</t>
         </is>
@@ -7059,44 +7063,44 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B3" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>GABALLAH B</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>GABALLAH B  (24H)</t>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>LI  (24H)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>AHLUWALIA Sa</t>
         </is>
       </c>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>LI A</t>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>GABALLAH</t>
         </is>
       </c>
     </row>
@@ -7109,19 +7113,19 @@
       <c r="B5" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>GABALLAH B, AHLUWALIA Sa</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>LI A</t>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>LI, AHLUWALIA Sa</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>GABALLAH</t>
         </is>
       </c>
     </row>
@@ -7134,19 +7138,19 @@
       <c r="B6" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>GABALLAH B</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I, AHLUWALIA Sa</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>LI A</t>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON, AHLUWALIA Sa</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>GABALLAH</t>
         </is>
       </c>
     </row>
@@ -7159,19 +7163,19 @@
       <c r="B7" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>AHLUWALIA Sa</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I, GABALLAH B</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>LI A</t>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON, LI</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>GABALLAH</t>
         </is>
       </c>
     </row>
@@ -7184,19 +7188,19 @@
       <c r="B8" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>GABALLAH B</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>LI A</t>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>GABALLAH</t>
         </is>
       </c>
     </row>
@@ -7209,61 +7213,61 @@
       <c r="B9" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>GABALLAH B, AHLUWALIA Sa</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>LI A</t>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON, AHLUWALIA Sa</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>GABALLAH</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B10" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>AHLUWALIA Sa</t>
         </is>
       </c>
-      <c r="D10" s="4" t="n"/>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>AHLUWALIA Sa  (24H)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>GABALLAH B</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>LI</t>
         </is>
       </c>
     </row>
@@ -7276,19 +7280,19 @@
       <c r="B12" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>LI A</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>METRI N, AHLUWALIA Sa</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>METRI</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>AHLUWALIA Sa, BRONSON</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>LI</t>
         </is>
       </c>
     </row>
@@ -7301,19 +7305,19 @@
       <c r="B13" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>METRI N</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>LI A, AHLUWALIA Sa</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>AHLUWALIA Sa</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>METRI, BRONSON</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>LI</t>
         </is>
       </c>
     </row>
@@ -7326,19 +7330,19 @@
       <c r="B14" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>AHLUWALIA Sa</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>LI A, METRI N</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>METRI, AHLUWALIA Sa</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>LI</t>
         </is>
       </c>
     </row>
@@ -7351,19 +7355,19 @@
       <c r="B15" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>METRI N</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>METRI</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>AHLUWALIA Sa</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>LI</t>
         </is>
       </c>
     </row>
@@ -7376,61 +7380,61 @@
       <c r="B16" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>LI A</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>METRI N, AHLUWALIA Sa</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>AHLUWALIA Sa</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>METRI, BRONSON</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>LI</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B17" s="4" t="n">
+      <c r="B17" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>BRONSON  (24H)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>SUNDAY</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>METRI</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="inlineStr">
         <is>
           <t>AHLUWALIA Sa</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="n"/>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>AHLUWALIA Sa  (24H)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>SUNDAY</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>METRI N</t>
         </is>
       </c>
     </row>
@@ -7443,19 +7447,19 @@
       <c r="B19" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>LI A</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I, SANCHEZ-ALMANZAR D</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>METRI N</t>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON, METRI</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>SANCHEZ-ALMANZAR</t>
         </is>
       </c>
     </row>
@@ -7468,19 +7472,19 @@
       <c r="B20" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>SANCHEZ-ALMANZAR D</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>LI A, BRONSON I</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>METRI N</t>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>LI, METRI</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>SANCHEZ-ALMANZAR</t>
         </is>
       </c>
     </row>
@@ -7493,19 +7497,19 @@
       <c r="B21" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>LI A, SANCHEZ-ALMANZAR D</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>METRI N</t>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>METRI</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>LI, BRONSON</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>SANCHEZ-ALMANZAR</t>
         </is>
       </c>
     </row>
@@ -7518,19 +7522,19 @@
       <c r="B22" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>SANCHEZ-ALMANZAR D</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>METRI N</t>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>SANCHEZ-ALMANZAR</t>
         </is>
       </c>
     </row>
@@ -7543,61 +7547,61 @@
       <c r="B23" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>LI A, SANCHEZ-ALMANZAR D</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>METRI N</t>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>LI, METRI</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>SANCHEZ-ALMANZAR</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B24" s="4" t="n">
+      <c r="B24" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>LI A</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="n"/>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>LI A  (24H)</t>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>METRI</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>METRI  (24H)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="B25" s="5" t="n">
+      <c r="B25" s="6" t="n">
         <v>23</v>
       </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>METRI N</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>SANCHEZ-ALMANZAR D</t>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
         </is>
       </c>
     </row>
@@ -7610,19 +7614,19 @@
       <c r="B26" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>LI A, SAEED S</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>SANCHEZ-ALMANZAR D</t>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>SANCHEZ-ALMANZAR</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>SAEED Sh, LI</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
         </is>
       </c>
     </row>
@@ -7635,19 +7639,19 @@
       <c r="B27" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>SAEED S</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>LI A, BRONSON I</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>SANCHEZ-ALMANZAR D</t>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>SAEED Sh</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>SANCHEZ-ALMANZAR, LI</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
         </is>
       </c>
     </row>
@@ -7660,19 +7664,19 @@
       <c r="B28" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>LI A</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I, SAEED S</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>SANCHEZ-ALMANZAR D</t>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>SANCHEZ-ALMANZAR, SAEED Sh</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
         </is>
       </c>
     </row>
@@ -7685,19 +7689,19 @@
       <c r="B29" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>SAEED S</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>SANCHEZ-ALMANZAR D</t>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>SANCHEZ-ALMANZAR</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>SAEED Sh</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
         </is>
       </c>
     </row>
@@ -7710,61 +7714,61 @@
       <c r="B30" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>SAEED S</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>LI A, BRONSON I</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>SANCHEZ-ALMANZAR D</t>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>SAEED Sh</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>SANCHEZ-ALMANZAR, LI</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B31" s="4" t="n">
+      <c r="B31" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="n"/>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>BRONSON I  (24H)</t>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="n"/>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>LI  (24H)</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="B32" s="5" t="n">
+      <c r="B32" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>SANCHEZ-ALMANZAR D</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="n"/>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>SAEED S</t>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>SANCHEZ-ALMANZAR</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>SAEED Sh</t>
         </is>
       </c>
     </row>
@@ -7777,36 +7781,36 @@
       <c r="B33" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>LI A</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I, SANCHEZ-ALMANZAR D</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>SAEED S</t>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>LI, SANCHEZ-ALMANZAR</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>SAEED Sh</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>INTERNS</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D35" s="7" t="inlineStr">
         <is>
           <t>DATES</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>LSH</t>
         </is>
@@ -7837,7 +7841,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="C40" s="6" t="inlineStr">
+      <c r="C40" s="7" t="inlineStr">
         <is>
           <t>BMC-S / BRIGHTON</t>
         </is>
@@ -7880,7 +7884,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="C45" s="6" t="inlineStr">
+      <c r="C45" s="7" t="inlineStr">
         <is>
           <t>LAHEY</t>
         </is>
@@ -7911,7 +7915,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="C49" s="6" t="inlineStr">
+      <c r="C49" s="7" t="inlineStr">
         <is>
           <t>SENIOR RESIDENT</t>
         </is>
@@ -7954,7 +7958,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="C54" s="7" t="inlineStr">
+      <c r="C54" s="8" t="inlineStr">
         <is>
           <t>SHORT CALL DOESN'T LEAVE BEFORE 4 PM, UNLESS APPROVED BY PD/APDS</t>
         </is>
@@ -8026,19 +8030,19 @@
       <c r="B3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>MATSUOKA K</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O, SANCHEZ-ALMANZAR D</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>SAEED S</t>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>MATSUOKA, SANCHEZ-ALMANZAR</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>SAEED Sh</t>
         </is>
       </c>
     </row>
@@ -8051,19 +8055,19 @@
       <c r="B4" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>MATSUOKA K, SANCHEZ-ALMANZAR D</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>SAEED S</t>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>SANCHEZ-ALMANZAR</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>MATSUOKA, OGHENESUME</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>SAEED Sh</t>
         </is>
       </c>
     </row>
@@ -8076,19 +8080,19 @@
       <c r="B5" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>SANCHEZ-ALMANZAR D</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>SAEED S</t>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>MATSUOKA</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>SAEED Sh</t>
         </is>
       </c>
     </row>
@@ -8101,61 +8105,61 @@
       <c r="B6" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>MATSUOKA K, SANCHEZ-ALMANZAR D</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>SAEED S</t>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>MATSUOKA, SANCHEZ-ALMANZAR</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>SAEED Sh</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>MATSUOKA K</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>MATSUOKA K  (24H)</t>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>SANCHEZ-ALMANZAR</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>SANCHEZ-ALMANZAR  (24H)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>SANCHEZ-ALMANZAR D</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>OGHENESUME O</t>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>MATSUOKA</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
         </is>
       </c>
     </row>
@@ -8168,19 +8172,19 @@
       <c r="B9" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>SAEED S</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>MATSUOKA K, SANCHEZ-ALMANZAR D</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O</t>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>SAEED Sh</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>SANCHEZ-ALMANZAR, MATSUOKA</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
         </is>
       </c>
     </row>
@@ -8193,19 +8197,19 @@
       <c r="B10" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>MATSUOKA K</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>SAEED S, SANCHEZ-ALMANZAR D</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O</t>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>SANCHEZ-ALMANZAR</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>SAEED Sh, MATSUOKA</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
         </is>
       </c>
     </row>
@@ -8218,19 +8222,19 @@
       <c r="B11" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>SANCHEZ-ALMANZAR D</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>MATSUOKA K, SAEED S</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O</t>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>MATSUOKA</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>SAEED Sh, SANCHEZ-ALMANZAR</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
         </is>
       </c>
     </row>
@@ -8243,19 +8247,19 @@
       <c r="B12" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>SAEED S</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>MATSUOKA K</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O</t>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>SAEED Sh</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>SANCHEZ-ALMANZAR</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
         </is>
       </c>
     </row>
@@ -8268,61 +8272,61 @@
       <c r="B13" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>MATSUOKA K</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>SAEED S, SANCHEZ-ALMANZAR D</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O</t>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>SANCHEZ-ALMANZAR</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>SAEED Sh, MATSUOKA</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>SANCHEZ-ALMANZAR D</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="n"/>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>SANCHEZ-ALMANZAR D  (24H)</t>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>MATSUOKA</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>MATSUOKA  (24H)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B15" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>SAEED S</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>MATSUOKA K</t>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>SAEED Sh</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>SANCHEZ-ALMANZAR</t>
         </is>
       </c>
     </row>
@@ -8335,19 +8339,19 @@
       <c r="B16" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>SAEED S, PATEL T</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>MATSUOKA K</t>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>MATSUOKA, SAEED Sh</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>PATEL</t>
         </is>
       </c>
     </row>
@@ -8360,19 +8364,19 @@
       <c r="B17" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>PATEL T</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O, SAEED S</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>MATSUOKA K</t>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>MATSUOKA</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME, SAEED Sh</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>PATEL</t>
         </is>
       </c>
     </row>
@@ -8385,19 +8389,19 @@
       <c r="B18" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>SAEED S</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O, PATEL T</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>MATSUOKA K</t>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>SAEED Sh</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME, MATSUOKA</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>PATEL</t>
         </is>
       </c>
     </row>
@@ -8410,19 +8414,19 @@
       <c r="B19" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>PATEL T</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>SAEED S</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>MATSUOKA K</t>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>MATSUOKA</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>PATEL</t>
         </is>
       </c>
     </row>
@@ -8435,61 +8439,61 @@
       <c r="B20" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>SAEED S</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O, PATEL T</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>MATSUOKA K</t>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>MATSUOKA</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME, SAEED Sh</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>PATEL</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B21" s="4" t="n">
+      <c r="B21" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>OGHENESUME O</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>OGHENESUME O  (24H)</t>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>SAEED Sh</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>SAEED Sh  (24H)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="B22" s="5" t="n">
+      <c r="B22" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>SAEED S</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>PATEL T</t>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>MATSUOKA</t>
         </is>
       </c>
     </row>
@@ -8502,19 +8506,19 @@
       <c r="B23" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>MATSUOKA K</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>PATEL T</t>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>PATEL</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>MATSUOKA</t>
         </is>
       </c>
     </row>
@@ -8527,19 +8531,19 @@
       <c r="B24" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>MATSUOKA K</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>PATEL T</t>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>PATEL</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>MATSUOKA</t>
         </is>
       </c>
     </row>
@@ -8552,36 +8556,36 @@
       <c r="B25" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>MATSUOKA K</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>PATEL T</t>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>PATEL</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>MATSUOKA</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>INTERNS</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t>DATES</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>LSH</t>
         </is>
@@ -8612,7 +8616,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>BMC-S / BRIGHTON</t>
         </is>
@@ -8631,7 +8635,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>LAHEY</t>
         </is>
@@ -8662,7 +8666,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="C39" s="6" t="inlineStr">
+      <c r="C39" s="7" t="inlineStr">
         <is>
           <t>SENIOR RESIDENT</t>
         </is>
@@ -8693,7 +8697,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="C43" s="7" t="inlineStr">
+      <c r="C43" s="8" t="inlineStr">
         <is>
           <t>SHORT CALL DOESN'T LEAVE BEFORE 4 PM, UNLESS APPROVED BY PD/APDS</t>
         </is>

--- a/intern_schedule_2026-2027/schedules/TYP_Intern_Schedule_Oct2026-Jun2027.xlsx
+++ b/intern_schedule_2026-2027/schedules/TYP_Intern_Schedule_Oct2026-Jun2027.xlsx
@@ -1474,7 +1474,7 @@
       <c r="D3" s="6" t="n"/>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -1494,12 +1494,12 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY, MULLINS</t>
+          <t>CHIASSON, MULLINS</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -1514,17 +1514,17 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
+          <t>CHIASSON</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>WISE, MULLINS</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
           <t>KENNEDY</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>WISE, MULLINS</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>CHIASSON</t>
         </is>
       </c>
     </row>
@@ -1544,12 +1544,12 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>WISE, KENNEDY</t>
+          <t>WISE, CHIASSON</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -1569,12 +1569,12 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>CHIASSON</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
           <t>KENNEDY</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>CHIASSON</t>
         </is>
       </c>
     </row>
@@ -1589,17 +1589,17 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
+          <t>CHIASSON</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>WISE, MULLINS</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
           <t>KENNEDY</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>WISE, MULLINS</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>CHIASSON</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       <c r="D10" s="6" t="n"/>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>CHIASSON</t>
         </is>
       </c>
     </row>
@@ -1656,17 +1656,17 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>SAEED U, WISE</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
           <t>CHIASSON</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>SAEED U, WISE</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -1686,12 +1686,12 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>CHIASSON, WISE</t>
+          <t>KENNEDY, WISE</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>CHIASSON</t>
         </is>
       </c>
     </row>
@@ -1711,12 +1711,12 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>CHIASSON, SAEED U</t>
+          <t>KENNEDY, SAEED U</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>CHIASSON</t>
         </is>
       </c>
     </row>
@@ -1731,17 +1731,17 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>SAEED U</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
           <t>CHIASSON</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>SAEED U</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>CHIASSON, WISE</t>
+          <t>KENNEDY, WISE</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>CHIASSON</t>
         </is>
       </c>
     </row>

--- a/intern_schedule_2026-2027/schedules/TYP_Intern_Schedule_Oct2026-Jun2027.xlsx
+++ b/intern_schedule_2026-2027/schedules/TYP_Intern_Schedule_Oct2026-Jun2027.xlsx
@@ -1474,7 +1474,7 @@
       <c r="D3" s="6" t="n"/>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>CHIASSON</t>
         </is>
       </c>
     </row>
@@ -1494,12 +1494,12 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>CHIASSON, MULLINS</t>
+          <t>KENNEDY, MULLINS</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>CHIASSON</t>
         </is>
       </c>
     </row>
@@ -1514,17 +1514,17 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>WISE, MULLINS</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
           <t>CHIASSON</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>WISE, MULLINS</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -1544,12 +1544,12 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>WISE, CHIASSON</t>
+          <t>WISE, KENNEDY</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>CHIASSON</t>
         </is>
       </c>
     </row>
@@ -1569,12 +1569,12 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
           <t>CHIASSON</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -1589,17 +1589,17 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>WISE, MULLINS</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
           <t>CHIASSON</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>WISE, MULLINS</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       <c r="D10" s="6" t="n"/>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -1656,17 +1656,17 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
+          <t>CHIASSON</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>SAEED U, WISE</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
           <t>KENNEDY</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>SAEED U, WISE</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>CHIASSON</t>
         </is>
       </c>
     </row>
@@ -1686,12 +1686,12 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY, WISE</t>
+          <t>CHIASSON, WISE</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -1711,12 +1711,12 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY, SAEED U</t>
+          <t>CHIASSON, SAEED U</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -1731,17 +1731,17 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
+          <t>CHIASSON</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>SAEED U</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
           <t>KENNEDY</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>SAEED U</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>CHIASSON</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY, WISE</t>
+          <t>CHIASSON, WISE</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>

--- a/intern_schedule_2026-2027/schedules/TYP_Intern_Schedule_Oct2026-Jun2027.xlsx
+++ b/intern_schedule_2026-2027/schedules/TYP_Intern_Schedule_Oct2026-Jun2027.xlsx
@@ -3361,12 +3361,12 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>ZAIDI</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>ZAIDI, FARZEELA</t>
+          <t>OGHENESUME, FARZEELA</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -3407,13 +3407,13 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>OGHENESUME</t>
         </is>
       </c>
       <c r="D5" s="6" t="n"/>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>ZAIDI</t>
         </is>
       </c>
     </row>
@@ -3433,12 +3433,12 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>AHN, ZAIDI</t>
+          <t>AHN, OGHENESUME</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>ZAIDI</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>SALAM, ZAIDI</t>
+          <t>SALAM, OGHENESUME</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>ZAIDI</t>
         </is>
       </c>
     </row>
@@ -3478,17 +3478,17 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
+          <t>OGHENESUME</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>SALAM, AHN</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
           <t>ZAIDI</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>SALAM, AHN</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>OGHENESUME</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>ZAIDI</t>
         </is>
       </c>
     </row>
@@ -3533,12 +3533,12 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>SALAM, ZAIDI</t>
+          <t>SALAM, OGHENESUME</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>ZAIDI</t>
         </is>
       </c>
     </row>
@@ -3553,13 +3553,13 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>OGHENESUME</t>
         </is>
       </c>
       <c r="D11" s="5" t="n"/>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>ZAIDI  (24H)</t>
+          <t>OGHENESUME  (24H)</t>
         </is>
       </c>
     </row>
@@ -3595,12 +3595,12 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>ZAIDI</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>ZAIDI, JUYAL</t>
+          <t>OGHENESUME, JUYAL</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -3620,12 +3620,12 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>OGHENESUME</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>OGHENESUME, JUYAL</t>
+          <t>ZAIDI, JUYAL</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>OGHENESUME, ZAIDI</t>
+          <t>ZAIDI, OGHENESUME</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -3670,12 +3670,12 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
+          <t>ZAIDI</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
           <t>OGHENESUME</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>ZAIDI</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>OGHENESUME</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>OGHENESUME, JUYAL</t>
+          <t>ZAIDI, JUYAL</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -3741,13 +3741,13 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>ZAIDI</t>
         </is>
       </c>
       <c r="D19" s="6" t="n"/>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>OGHENESUME</t>
         </is>
       </c>
     </row>
@@ -3767,12 +3767,12 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>JUYAL, OGHENESUME</t>
+          <t>JUYAL, ZAIDI</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>OGHENESUME</t>
         </is>
       </c>
     </row>
@@ -3792,12 +3792,12 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>AHN, OGHENESUME</t>
+          <t>AHN, ZAIDI</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>OGHENESUME</t>
         </is>
       </c>
     </row>
@@ -3812,17 +3812,17 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
+          <t>ZAIDI</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>AHN, JUYAL</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
           <t>OGHENESUME</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>AHN, JUYAL</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>ZAIDI</t>
         </is>
       </c>
     </row>
@@ -3847,7 +3847,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>OGHENESUME</t>
         </is>
       </c>
     </row>
@@ -3867,12 +3867,12 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>AHN, OGHENESUME</t>
+          <t>AHN, ZAIDI</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>OGHENESUME</t>
         </is>
       </c>
     </row>
@@ -3887,13 +3887,13 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>ZAIDI</t>
         </is>
       </c>
       <c r="D25" s="5" t="n"/>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>OGHENESUME  (24H)</t>
+          <t>ZAIDI  (24H)</t>
         </is>
       </c>
     </row>
@@ -3929,12 +3929,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>OGHENESUME</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>OGHENESUME, AHN</t>
+          <t>ZAIDI, AHN</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>ZAIDI</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>ZAIDI, AHN</t>
+          <t>OGHENESUME, AHN</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>ZAIDI, OGHENESUME</t>
+          <t>OGHENESUME, ZAIDI</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -4004,12 +4004,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
+          <t>OGHENESUME</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
           <t>ZAIDI</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>OGHENESUME</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -4029,12 +4029,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>ZAIDI</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>ZAIDI, AHN</t>
+          <t>OGHENESUME, AHN</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -4075,13 +4075,13 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>OGHENESUME</t>
         </is>
       </c>
       <c r="D33" s="6" t="n"/>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>ZAIDI</t>
         </is>
       </c>
     </row>
@@ -4107,7 +4107,7 @@
     <row r="37">
       <c r="C37" t="inlineStr">
         <is>
-          <t>Humza Zaidi</t>
+          <t>Oghenewoma Oghenesume</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4119,7 +4119,7 @@
     <row r="38">
       <c r="C38" t="inlineStr">
         <is>
-          <t>Oghenewoma Oghenesume</t>
+          <t>Humza Zaidi</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4301,12 +4301,12 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>FARZEELA, ZAIDI</t>
+          <t>FARZEELA, LI</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>ZAIDI</t>
         </is>
       </c>
     </row>
@@ -4326,12 +4326,12 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>JUYAL, ZAIDI</t>
+          <t>JUYAL, LI</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>ZAIDI</t>
         </is>
       </c>
     </row>
@@ -4346,17 +4346,17 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>JUYAL, FARZEELA</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
           <t>ZAIDI</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>JUYAL, FARZEELA</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>LI</t>
         </is>
       </c>
     </row>
@@ -4381,7 +4381,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>ZAIDI</t>
         </is>
       </c>
     </row>
@@ -4401,12 +4401,12 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>JUYAL, ZAIDI</t>
+          <t>JUYAL, LI</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>ZAIDI</t>
         </is>
       </c>
     </row>
@@ -4421,13 +4421,13 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>LI</t>
         </is>
       </c>
       <c r="D8" s="5" t="n"/>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>ZAIDI  (24H)</t>
+          <t>LI  (24H)</t>
         </is>
       </c>
     </row>
@@ -4463,12 +4463,12 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>ZAIDI</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>ZAIDI, KOPP VANUZZI</t>
+          <t>LI, KOPP VANUZZI</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -4488,12 +4488,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>LI</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>LI, KOPP VANUZZI</t>
+          <t>ZAIDI, KOPP VANUZZI</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>LI, ZAIDI</t>
+          <t>ZAIDI, LI</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
+          <t>ZAIDI</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
           <t>LI</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>ZAIDI</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -4563,12 +4563,12 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>LI</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>LI, KOPP VANUZZI</t>
+          <t>ZAIDI, KOPP VANUZZI</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -4609,13 +4609,13 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>ZAIDI</t>
         </is>
       </c>
       <c r="D16" s="6" t="n"/>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>LI</t>
         </is>
       </c>
     </row>
@@ -4635,12 +4635,12 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI, LI</t>
+          <t>KOPP VANUZZI, ZAIDI</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>LI</t>
         </is>
       </c>
     </row>
@@ -4660,12 +4660,12 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>VILLANUEVA, LI</t>
+          <t>VILLANUEVA, ZAIDI</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>LI</t>
         </is>
       </c>
     </row>
@@ -4680,17 +4680,17 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
+          <t>ZAIDI</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>VILLANUEVA, KOPP VANUZZI</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
           <t>LI</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>VILLANUEVA, KOPP VANUZZI</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>ZAIDI</t>
         </is>
       </c>
     </row>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>LI</t>
         </is>
       </c>
     </row>
@@ -4735,12 +4735,12 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>VILLANUEVA, LI</t>
+          <t>VILLANUEVA, ZAIDI</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>LI</t>
         </is>
       </c>
     </row>
@@ -4755,13 +4755,13 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>ZAIDI</t>
         </is>
       </c>
       <c r="D22" s="5" t="n"/>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>LI  (24H)</t>
+          <t>ZAIDI  (24H)</t>
         </is>
       </c>
     </row>
@@ -4797,12 +4797,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>LI</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>LI, VILLANUEVA</t>
+          <t>ZAIDI, VILLANUEVA</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -4822,12 +4822,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>ZAIDI</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>ZAIDI, VILLANUEVA</t>
+          <t>LI, VILLANUEVA</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>ZAIDI, LI</t>
+          <t>LI, ZAIDI</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
           <t>ZAIDI</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>LI</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>ZAIDI</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>ZAIDI, VILLANUEVA</t>
+          <t>LI, VILLANUEVA</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -4943,13 +4943,13 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>LI</t>
         </is>
       </c>
       <c r="D30" s="6" t="n"/>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>ZAIDI</t>
         </is>
       </c>
     </row>
@@ -4975,7 +4975,7 @@
     <row r="34">
       <c r="C34" t="inlineStr">
         <is>
-          <t>Humza Zaidi</t>
+          <t>Anna Li</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4987,7 +4987,7 @@
     <row r="35">
       <c r="C35" t="inlineStr">
         <is>
-          <t>Anna Li</t>
+          <t>Humza Zaidi</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>SHETTY, KENNEDY</t>
+          <t>SHETTY, MATSUOKA</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -5194,12 +5194,12 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI, KENNEDY</t>
+          <t>KOPP VANUZZI, MATSUOKA</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -5214,17 +5214,17 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
+          <t>MATSUOKA</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>KOPP VANUZZI, SHETTY</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
           <t>KENNEDY</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>KOPP VANUZZI, SHETTY</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>MATSUOKA</t>
         </is>
       </c>
     </row>
@@ -5249,7 +5249,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -5269,12 +5269,12 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI, KENNEDY</t>
+          <t>KOPP VANUZZI, MATSUOKA</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -5289,13 +5289,13 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>MATSUOKA</t>
         </is>
       </c>
       <c r="D8" s="5" t="n"/>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>KENNEDY  (24H)</t>
+          <t>MATSUOKA  (24H)</t>
         </is>
       </c>
     </row>
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>KENNEDY</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY, PATEL</t>
+          <t>MATSUOKA, PATEL</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>MATSUOKA</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>MATSUOKA, PATEL</t>
+          <t>KENNEDY, PATEL</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>MATSUOKA, KENNEDY</t>
+          <t>KENNEDY, MATSUOKA</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -5406,12 +5406,12 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
           <t>MATSUOKA</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>KENNEDY</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>MATSUOKA</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>MATSUOKA, PATEL</t>
+          <t>KENNEDY, PATEL</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -5477,13 +5477,13 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>KENNEDY</t>
         </is>
       </c>
       <c r="D16" s="6" t="n"/>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>MATSUOKA</t>
         </is>
       </c>
     </row>
@@ -5503,12 +5503,12 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>PATEL, MATSUOKA</t>
+          <t>PATEL, KENNEDY</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>MATSUOKA</t>
         </is>
       </c>
     </row>
@@ -5528,12 +5528,12 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>BUTT, MATSUOKA</t>
+          <t>BUTT, KENNEDY</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>MATSUOKA</t>
         </is>
       </c>
     </row>
@@ -5548,17 +5548,17 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>BUTT, PATEL</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
           <t>MATSUOKA</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>BUTT, PATEL</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>MATSUOKA</t>
         </is>
       </c>
     </row>
@@ -5603,12 +5603,12 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>BUTT, MATSUOKA</t>
+          <t>BUTT, KENNEDY</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>MATSUOKA</t>
         </is>
       </c>
     </row>
@@ -5623,13 +5623,13 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>KENNEDY</t>
         </is>
       </c>
       <c r="D22" s="5" t="n"/>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>MATSUOKA  (24H)</t>
+          <t>KENNEDY  (24H)</t>
         </is>
       </c>
     </row>
@@ -5665,12 +5665,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>MATSUOKA</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>MATSUOKA, BUTT</t>
+          <t>KENNEDY, BUTT</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>KENNEDY</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY, BUTT</t>
+          <t>MATSUOKA, BUTT</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -5720,7 +5720,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY, MATSUOKA</t>
+          <t>MATSUOKA, KENNEDY</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
+          <t>MATSUOKA</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
           <t>KENNEDY</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>MATSUOKA</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -5765,12 +5765,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>KENNEDY</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY, BUTT</t>
+          <t>MATSUOKA, BUTT</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -5811,13 +5811,13 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>MATSUOKA</t>
         </is>
       </c>
       <c r="D30" s="6" t="n"/>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -5837,12 +5837,12 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>RIVERA, KENNEDY</t>
+          <t>RIVERA, MATSUOKA</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -5862,12 +5862,12 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>ALMADHOOB, KENNEDY</t>
+          <t>ALMADHOOB, MATSUOKA</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>MATSUOKA</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -5882,17 +5882,17 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
+          <t>MATSUOKA</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>ALMADHOOB, RIVERA</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
           <t>KENNEDY</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>ALMADHOOB, RIVERA</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>MATSUOKA</t>
         </is>
       </c>
     </row>
@@ -5918,7 +5918,7 @@
     <row r="37">
       <c r="C37" t="inlineStr">
         <is>
-          <t>Dean Kennedy</t>
+          <t>Kazune Matsuoka</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5930,7 +5930,7 @@
     <row r="38">
       <c r="C38" t="inlineStr">
         <is>
-          <t>Kazune Matsuoka</t>
+          <t>Dean Kennedy</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">

--- a/intern_schedule_2026-2027/schedules/TYP_Intern_Schedule_Oct2026-Jun2027.xlsx
+++ b/intern_schedule_2026-2027/schedules/TYP_Intern_Schedule_Oct2026-Jun2027.xlsx
@@ -4463,12 +4463,12 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>KOPP VANUZZI</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>LI, KOPP VANUZZI</t>
+          <t>LI, ZAIDI</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -4493,7 +4493,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>ZAIDI, KOPP VANUZZI</t>
+          <t>KOPP VANUZZI, ZAIDI</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI</t>
+          <t>ZAIDI</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>ZAIDI, LI</t>
+          <t>KOPP VANUZZI, LI</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>KOPP VANUZZI</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>ZAIDI, KOPP VANUZZI</t>
+          <t>KOPP VANUZZI, ZAIDI</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -4588,13 +4588,13 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI</t>
+          <t>ZAIDI</t>
         </is>
       </c>
       <c r="D15" s="5" t="n"/>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI  (24H)</t>
+          <t>ZAIDI  (24H)</t>
         </is>
       </c>
     </row>
@@ -4609,7 +4609,7 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>KOPP VANUZZI</t>
         </is>
       </c>
       <c r="D16" s="6" t="n"/>
@@ -4635,7 +4635,7 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI, ZAIDI</t>
+          <t>ZAIDI, KOPP VANUZZI</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI</t>
+          <t>ZAIDI</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>VILLANUEVA, ZAIDI</t>
+          <t>VILLANUEVA, KOPP VANUZZI</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -4680,12 +4680,12 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>KOPP VANUZZI</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>VILLANUEVA, KOPP VANUZZI</t>
+          <t>VILLANUEVA, ZAIDI</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI</t>
+          <t>ZAIDI</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -4730,12 +4730,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI</t>
+          <t>ZAIDI</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>VILLANUEVA, ZAIDI</t>
+          <t>VILLANUEVA, KOPP VANUZZI</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -4755,13 +4755,13 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>KOPP VANUZZI</t>
         </is>
       </c>
       <c r="D22" s="5" t="n"/>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>ZAIDI  (24H)</t>
+          <t>KOPP VANUZZI  (24H)</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4782,7 @@
       <c r="D23" s="6" t="n"/>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI</t>
+          <t>ZAIDI</t>
         </is>
       </c>
     </row>
@@ -4802,12 +4802,12 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>ZAIDI, VILLANUEVA</t>
+          <t>KOPP VANUZZI, VILLANUEVA</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI</t>
+          <t>ZAIDI</t>
         </is>
       </c>
     </row>
@@ -4822,17 +4822,17 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
+          <t>KOPP VANUZZI</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>LI, VILLANUEVA</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
           <t>ZAIDI</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>LI, VILLANUEVA</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>KOPP VANUZZI</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>LI, ZAIDI</t>
+          <t>LI, KOPP VANUZZI</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI</t>
+          <t>ZAIDI</t>
         </is>
       </c>
     </row>
@@ -4877,12 +4877,12 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
+          <t>KOPP VANUZZI</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
           <t>ZAIDI</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>KOPP VANUZZI</t>
         </is>
       </c>
     </row>
@@ -4897,17 +4897,17 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
+          <t>KOPP VANUZZI</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>LI, VILLANUEVA</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
           <t>ZAIDI</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>LI, VILLANUEVA</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>KOPP VANUZZI</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       <c r="D30" s="6" t="n"/>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>KOPP VANUZZI</t>
         </is>
       </c>
     </row>
@@ -5164,17 +5164,17 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>SHETTY, MATSUOKA</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
           <t>KOPP VANUZZI</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>SHETTY, MATSUOKA</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -5194,12 +5194,12 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI, MATSUOKA</t>
+          <t>KENNEDY, MATSUOKA</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>KOPP VANUZZI</t>
         </is>
       </c>
     </row>
@@ -5219,12 +5219,12 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI, SHETTY</t>
+          <t>KENNEDY, SHETTY</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>KOPP VANUZZI</t>
         </is>
       </c>
     </row>
@@ -5239,17 +5239,17 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>SHETTY</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
           <t>KOPP VANUZZI</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>SHETTY</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -5269,12 +5269,12 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI, MATSUOKA</t>
+          <t>KENNEDY, MATSUOKA</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>KOPP VANUZZI</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI</t>
+          <t>KENNEDY</t>
         </is>
       </c>
       <c r="D9" s="6" t="n"/>
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>PATEL</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>MATSUOKA, PATEL</t>
+          <t>MATSUOKA, KENNEDY</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY, PATEL</t>
+          <t>PATEL, KENNEDY</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -5381,12 +5381,12 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>PATEL</t>
+          <t>KENNEDY</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY, MATSUOKA</t>
+          <t>PATEL, MATSUOKA</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>PATEL</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -5436,7 +5436,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY, PATEL</t>
+          <t>PATEL, KENNEDY</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -5456,13 +5456,13 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>PATEL</t>
+          <t>KENNEDY</t>
         </is>
       </c>
       <c r="D15" s="5" t="n"/>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>PATEL  (24H)</t>
+          <t>KENNEDY  (24H)</t>
         </is>
       </c>
     </row>
@@ -5477,7 +5477,7 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>PATEL</t>
         </is>
       </c>
       <c r="D16" s="6" t="n"/>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>PATEL, KENNEDY</t>
+          <t>KENNEDY, PATEL</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>PATEL</t>
+          <t>KENNEDY</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>BUTT, KENNEDY</t>
+          <t>BUTT, PATEL</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -5548,12 +5548,12 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>PATEL</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>BUTT, PATEL</t>
+          <t>BUTT, KENNEDY</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -5578,7 +5578,7 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>PATEL</t>
+          <t>KENNEDY</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>PATEL</t>
+          <t>KENNEDY</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>BUTT, KENNEDY</t>
+          <t>BUTT, PATEL</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -5623,13 +5623,13 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>PATEL</t>
         </is>
       </c>
       <c r="D22" s="5" t="n"/>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>KENNEDY  (24H)</t>
+          <t>PATEL  (24H)</t>
         </is>
       </c>
     </row>
@@ -5650,7 +5650,7 @@
       <c r="D23" s="6" t="n"/>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>PATEL</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -5670,12 +5670,12 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY, BUTT</t>
+          <t>ALMADHOOB, BUTT</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>ALMADHOOB</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -5690,17 +5690,17 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
+          <t>ALMADHOOB</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>MATSUOKA, BUTT</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
           <t>KENNEDY</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>MATSUOKA, BUTT</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>ALMADHOOB</t>
         </is>
       </c>
     </row>
@@ -5720,12 +5720,12 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>MATSUOKA, KENNEDY</t>
+          <t>MATSUOKA, ALMADHOOB</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>ALMADHOOB</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -5745,12 +5745,12 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
+          <t>ALMADHOOB</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
           <t>KENNEDY</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>ALMADHOOB</t>
         </is>
       </c>
     </row>
@@ -5765,17 +5765,17 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
+          <t>ALMADHOOB</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>MATSUOKA, BUTT</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
           <t>KENNEDY</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>MATSUOKA, BUTT</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>ALMADHOOB</t>
         </is>
       </c>
     </row>
@@ -5817,7 +5817,7 @@
       <c r="D30" s="6" t="n"/>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>ALMADHOOB</t>
         </is>
       </c>
     </row>
@@ -5832,17 +5832,17 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>RIVERA, MATSUOKA</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
           <t>ALMADHOOB</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>RIVERA, MATSUOKA</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -5862,12 +5862,12 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>ALMADHOOB, MATSUOKA</t>
+          <t>KENNEDY, MATSUOKA</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>ALMADHOOB</t>
         </is>
       </c>
     </row>
@@ -5887,12 +5887,12 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>ALMADHOOB, RIVERA</t>
+          <t>KENNEDY, RIVERA</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>ALMADHOOB</t>
         </is>
       </c>
     </row>
@@ -6143,17 +6143,17 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
+          <t>OGHENESUME</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>RIVERA</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
           <t>ALMADHOOB</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>RIVERA</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>OGHENESUME</t>
         </is>
       </c>
     </row>
@@ -6173,12 +6173,12 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>ALMADHOOB, ZAIDI</t>
+          <t>OGHENESUME, ZAIDI</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>ALMADHOOB</t>
         </is>
       </c>
     </row>
